--- a/research/traditional_assets/database/data/poland/poland_retail_general.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_retail_general.xlsx
@@ -1374,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1511,22 +1511,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09824681085235623</v>
+        <v>0.09813709191173678</v>
       </c>
       <c r="C2">
-        <v>31.92697128628497</v>
+        <v>31.67447588905083</v>
       </c>
       <c r="D2">
-        <v>31.91897128628497</v>
+        <v>31.98588588905083</v>
       </c>
       <c r="E2">
-        <v>-0.341</v>
+        <v>-0.02159</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.31941</v>
       </c>
       <c r="G2">
         <v>0.008</v>
@@ -1547,45 +1547,45 @@
         <v>0.099</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.017663373</v>
       </c>
       <c r="N2">
-        <v>0.099</v>
+        <v>0.08133662699999999</v>
       </c>
       <c r="O2">
-        <v>0.01881</v>
+        <v>0.01545395913</v>
       </c>
       <c r="P2">
-        <v>0.08019000000000001</v>
+        <v>0.06588266786999999</v>
       </c>
       <c r="Q2">
-        <v>-0.01880999999999999</v>
+        <v>-0.03311733213000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09824681085235623</v>
+        <v>0.09867592112296644</v>
       </c>
       <c r="T2">
-        <v>0.960581759320096</v>
+        <v>0.9684410646236242</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.0553</v>
       </c>
       <c r="V2">
         <v>0.19</v>
       </c>
       <c r="W2">
-        <v>0.040743</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>5.604818513428889</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1593,22 +1593,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09813709191173678</v>
+        <v>0.09835947297111729</v>
       </c>
       <c r="C3">
-        <v>31.67447588905083</v>
+        <v>31.21973243178538</v>
       </c>
       <c r="D3">
-        <v>31.98588588905083</v>
+        <v>31.85055243178538</v>
       </c>
       <c r="E3">
-        <v>-0.02159</v>
+        <v>0.29782</v>
       </c>
       <c r="F3">
-        <v>0.31941</v>
+        <v>0.6388200000000001</v>
       </c>
       <c r="G3">
         <v>0.008</v>
@@ -1629,45 +1629,45 @@
         <v>0.099</v>
       </c>
       <c r="M3">
-        <v>0.017663373</v>
+        <v>0.04842255600000001</v>
       </c>
       <c r="N3">
-        <v>0.08133662699999999</v>
+        <v>0.050577444</v>
       </c>
       <c r="O3">
-        <v>0.01545395913</v>
+        <v>0.00960971436</v>
       </c>
       <c r="P3">
-        <v>0.06588266786999999</v>
+        <v>0.04096772964</v>
       </c>
       <c r="Q3">
-        <v>-0.03311733213000001</v>
+        <v>-0.05803227036000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09867592112296644</v>
+        <v>0.09911378874603805</v>
       </c>
       <c r="T3">
-        <v>0.9684410646236242</v>
+        <v>0.9764607639129386</v>
       </c>
       <c r="U3">
-        <v>0.0553</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V3">
         <v>0.19</v>
       </c>
       <c r="W3">
-        <v>0.04479300000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y3">
-        <v>5.604818513428889</v>
+        <v>2.044501740056845</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1675,22 +1675,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09835947297111729</v>
+        <v>0.1021540986430343</v>
       </c>
       <c r="C4">
-        <v>31.21973243178538</v>
+        <v>28.755652801135</v>
       </c>
       <c r="D4">
-        <v>31.85055243178538</v>
+        <v>29.705882801135</v>
       </c>
       <c r="E4">
-        <v>0.29782</v>
+        <v>0.6172299999999999</v>
       </c>
       <c r="F4">
-        <v>0.6388200000000001</v>
+        <v>0.95823</v>
       </c>
       <c r="G4">
         <v>0.008</v>
@@ -1711,45 +1711,45 @@
         <v>0.099</v>
       </c>
       <c r="M4">
-        <v>0.04842255600000001</v>
+        <v>0.192412584</v>
       </c>
       <c r="N4">
-        <v>0.050577444</v>
+        <v>-0.09341258399999999</v>
       </c>
       <c r="O4">
-        <v>0.00960971436</v>
+        <v>-0.01774839096</v>
       </c>
       <c r="P4">
-        <v>0.04096772964</v>
+        <v>-0.07566419303999999</v>
       </c>
       <c r="Q4">
-        <v>-0.05803227036000001</v>
+        <v>-0.17466419304</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09911378874603805</v>
+        <v>0.0997103061074642</v>
       </c>
       <c r="T4">
-        <v>0.9764607639129386</v>
+        <v>0.9873861888757027</v>
       </c>
       <c r="U4">
-        <v>0.07580000000000001</v>
+        <v>0.2008</v>
       </c>
       <c r="V4">
-        <v>0.19</v>
+        <v>0.09775867881905272</v>
       </c>
       <c r="W4">
-        <v>0.06139800000000001</v>
+        <v>0.1811700572931342</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y4">
-        <v>2.044501740056845</v>
+        <v>0.5145193622055406</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1757,22 +1757,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1021540986430343</v>
+        <v>0.1051269293787597</v>
       </c>
       <c r="C5">
-        <v>28.755652801135</v>
+        <v>26.94770189150402</v>
       </c>
       <c r="D5">
-        <v>29.705882801135</v>
+        <v>28.21734189150402</v>
       </c>
       <c r="E5">
-        <v>0.6172299999999999</v>
+        <v>0.9366400000000001</v>
       </c>
       <c r="F5">
-        <v>0.95823</v>
+        <v>1.27764</v>
       </c>
       <c r="G5">
         <v>0.008</v>
@@ -1793,45 +1793,45 @@
         <v>0.099</v>
       </c>
       <c r="M5">
-        <v>0.192412584</v>
+        <v>0.301267512</v>
       </c>
       <c r="N5">
-        <v>-0.09341258399999999</v>
+        <v>-0.202267512</v>
       </c>
       <c r="O5">
-        <v>-0.01774839096</v>
+        <v>-0.03843082728</v>
       </c>
       <c r="P5">
-        <v>-0.07566419303999999</v>
+        <v>-0.16383668472</v>
       </c>
       <c r="Q5">
-        <v>-0.17466419304</v>
+        <v>-0.26283668472</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0997103061074642</v>
+        <v>0.1002956538124643</v>
       </c>
       <c r="T5">
-        <v>0.9873861888757027</v>
+        <v>0.9981070376584024</v>
       </c>
       <c r="U5">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>0.09775867881905272</v>
+        <v>0.06243620453837717</v>
       </c>
       <c r="W5">
-        <v>0.1811700572931342</v>
+        <v>0.2210775429698507</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y5">
-        <v>0.5145193622055406</v>
+        <v>0.3286116028335641</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1839,22 +1839,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1051269293787597</v>
+        <v>0.1070269293787597</v>
       </c>
       <c r="C6">
-        <v>26.94770189150402</v>
+        <v>25.7526486061418</v>
       </c>
       <c r="D6">
-        <v>28.21734189150402</v>
+        <v>27.3416986061418</v>
       </c>
       <c r="E6">
-        <v>0.9366400000000001</v>
+        <v>1.25605</v>
       </c>
       <c r="F6">
-        <v>1.27764</v>
+        <v>1.59705</v>
       </c>
       <c r="G6">
         <v>0.008</v>
@@ -1875,37 +1875,37 @@
         <v>0.099</v>
       </c>
       <c r="M6">
-        <v>0.301267512</v>
+        <v>0.3765843900000001</v>
       </c>
       <c r="N6">
-        <v>-0.202267512</v>
+        <v>-0.2775843900000001</v>
       </c>
       <c r="O6">
-        <v>-0.03843082728</v>
+        <v>-0.05274103410000002</v>
       </c>
       <c r="P6">
-        <v>-0.16383668472</v>
+        <v>-0.2248433559000001</v>
       </c>
       <c r="Q6">
-        <v>-0.26283668472</v>
+        <v>-0.3238433559000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1002956538124643</v>
+        <v>0.1008692922736481</v>
       </c>
       <c r="T6">
-        <v>0.9981070376584024</v>
+        <v>1.008613427528491</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>0.06243620453837717</v>
+        <v>0.04994896363070173</v>
       </c>
       <c r="W6">
-        <v>0.2210775429698507</v>
+        <v>0.2240220343758805</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>0.3286116028335641</v>
+        <v>0.2628892822668512</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1921,22 +1921,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1070269293787597</v>
+        <v>0.1089269293787597</v>
       </c>
       <c r="C7">
-        <v>25.7526486061418</v>
+        <v>24.61030570154928</v>
       </c>
       <c r="D7">
-        <v>27.3416986061418</v>
+        <v>26.51876570154928</v>
       </c>
       <c r="E7">
-        <v>1.25605</v>
+        <v>1.57546</v>
       </c>
       <c r="F7">
-        <v>1.59705</v>
+        <v>1.91646</v>
       </c>
       <c r="G7">
         <v>0.008</v>
@@ -1957,37 +1957,37 @@
         <v>0.099</v>
       </c>
       <c r="M7">
-        <v>0.3765843900000001</v>
+        <v>0.4519012680000001</v>
       </c>
       <c r="N7">
-        <v>-0.2775843900000001</v>
+        <v>-0.3529012680000001</v>
       </c>
       <c r="O7">
-        <v>-0.05274103410000002</v>
+        <v>-0.06705124092000002</v>
       </c>
       <c r="P7">
-        <v>-0.2248433559000001</v>
+        <v>-0.2858500270800001</v>
       </c>
       <c r="Q7">
-        <v>-0.3238433559000001</v>
+        <v>-0.38485002708</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1008692922736481</v>
+        <v>0.1014551358084742</v>
       </c>
       <c r="T7">
-        <v>1.008613427528491</v>
+        <v>1.019343357608581</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.04994896363070173</v>
+        <v>0.04162413635891812</v>
       </c>
       <c r="W7">
-        <v>0.2240220343758805</v>
+        <v>0.2259850286465671</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>0.2628892822668512</v>
+        <v>0.2190744018890426</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1089269293787597</v>
+        <v>0.1108269293787598</v>
       </c>
       <c r="C8">
-        <v>24.61030570154928</v>
+        <v>23.51605279701254</v>
       </c>
       <c r="D8">
-        <v>26.51876570154928</v>
+        <v>25.74392279701254</v>
       </c>
       <c r="E8">
-        <v>1.57546</v>
+        <v>1.89487</v>
       </c>
       <c r="F8">
-        <v>1.91646</v>
+        <v>2.23587</v>
       </c>
       <c r="G8">
         <v>0.008</v>
@@ -2039,37 +2039,37 @@
         <v>0.099</v>
       </c>
       <c r="M8">
-        <v>0.451901268</v>
+        <v>0.5272181459999999</v>
       </c>
       <c r="N8">
-        <v>-0.352901268</v>
+        <v>-0.428218146</v>
       </c>
       <c r="O8">
-        <v>-0.06705124092</v>
+        <v>-0.08136144774</v>
       </c>
       <c r="P8">
-        <v>-0.28585002708</v>
+        <v>-0.34685669826</v>
       </c>
       <c r="Q8">
-        <v>-0.3848500270799999</v>
+        <v>-0.44585669826</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1014551358084742</v>
+        <v>0.1020535781289954</v>
       </c>
       <c r="T8">
-        <v>1.019343357608581</v>
+        <v>1.03030403887319</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.04162413635891812</v>
+        <v>0.03567783116478696</v>
       </c>
       <c r="W8">
-        <v>0.2259850286465671</v>
+        <v>0.2273871674113432</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.2190744018890428</v>
+        <v>0.1877780587620366</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2085,22 +2085,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1108269293787597</v>
+        <v>0.1127269293787597</v>
       </c>
       <c r="C9">
-        <v>23.51605279701254</v>
+        <v>22.46579418691858</v>
       </c>
       <c r="D9">
-        <v>25.74392279701254</v>
+        <v>25.01307418691858</v>
       </c>
       <c r="E9">
-        <v>1.89487</v>
+        <v>2.21428</v>
       </c>
       <c r="F9">
-        <v>2.23587</v>
+        <v>2.55528</v>
       </c>
       <c r="G9">
         <v>0.008</v>
@@ -2121,37 +2121,37 @@
         <v>0.099</v>
       </c>
       <c r="M9">
-        <v>0.5272181460000001</v>
+        <v>0.602535024</v>
       </c>
       <c r="N9">
-        <v>-0.4282181460000001</v>
+        <v>-0.5035350240000001</v>
       </c>
       <c r="O9">
-        <v>-0.08136144774000001</v>
+        <v>-0.09567165456000001</v>
       </c>
       <c r="P9">
-        <v>-0.3468566982600001</v>
+        <v>-0.40786336944</v>
       </c>
       <c r="Q9">
-        <v>-0.4458566982600001</v>
+        <v>-0.50686336944</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1020535781289954</v>
+        <v>0.1026650300651801</v>
       </c>
       <c r="T9">
-        <v>1.03030403887319</v>
+        <v>1.041502995817463</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.03567783116478696</v>
+        <v>0.03121810226918859</v>
       </c>
       <c r="W9">
-        <v>0.2273871674113432</v>
+        <v>0.2284387714849253</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.1877780587620366</v>
+        <v>0.164305801416782</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2167,22 +2167,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1127269293787597</v>
+        <v>0.1146269293787597</v>
       </c>
       <c r="C10">
-        <v>22.46579418691858</v>
+        <v>21.45588642123136</v>
       </c>
       <c r="D10">
-        <v>25.01307418691858</v>
+        <v>24.32257642123136</v>
       </c>
       <c r="E10">
-        <v>2.21428</v>
+        <v>2.53369</v>
       </c>
       <c r="F10">
-        <v>2.55528</v>
+        <v>2.87469</v>
       </c>
       <c r="G10">
         <v>0.008</v>
@@ -2203,37 +2203,37 @@
         <v>0.099</v>
       </c>
       <c r="M10">
-        <v>0.602535024</v>
+        <v>0.6778519020000001</v>
       </c>
       <c r="N10">
-        <v>-0.5035350240000001</v>
+        <v>-0.5788519020000001</v>
       </c>
       <c r="O10">
-        <v>-0.09567165456000001</v>
+        <v>-0.10998186138</v>
       </c>
       <c r="P10">
-        <v>-0.40786336944</v>
+        <v>-0.4688700406200001</v>
       </c>
       <c r="Q10">
-        <v>-0.50686336944</v>
+        <v>-0.5678700406200001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1026650300651801</v>
+        <v>0.1032899205054568</v>
       </c>
       <c r="T10">
-        <v>1.041502995817463</v>
+        <v>1.052948083683589</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.03121810226918859</v>
+        <v>0.02774942423927874</v>
       </c>
       <c r="W10">
-        <v>0.2284387714849253</v>
+        <v>0.2292566857643781</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.164305801416782</v>
+        <v>0.1460496012593617</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2249,22 +2249,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1146269293787597</v>
+        <v>0.1165269293787597</v>
       </c>
       <c r="C11">
-        <v>21.45588642123136</v>
+        <v>20.48307755878593</v>
       </c>
       <c r="D11">
-        <v>24.32257642123136</v>
+        <v>23.66917755878593</v>
       </c>
       <c r="E11">
-        <v>2.53369</v>
+        <v>2.8531</v>
       </c>
       <c r="F11">
-        <v>2.87469</v>
+        <v>3.1941</v>
       </c>
       <c r="G11">
         <v>0.008</v>
@@ -2285,37 +2285,37 @@
         <v>0.099</v>
       </c>
       <c r="M11">
-        <v>0.6778519020000001</v>
+        <v>0.7531687800000001</v>
       </c>
       <c r="N11">
-        <v>-0.5788519020000001</v>
+        <v>-0.6541687800000001</v>
       </c>
       <c r="O11">
-        <v>-0.10998186138</v>
+        <v>-0.1242920682</v>
       </c>
       <c r="P11">
-        <v>-0.4688700406200001</v>
+        <v>-0.5298767118000001</v>
       </c>
       <c r="Q11">
-        <v>-0.5678700406200001</v>
+        <v>-0.6288767118</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1032899205054568</v>
+        <v>0.1039286973999619</v>
       </c>
       <c r="T11">
-        <v>1.052948083683589</v>
+        <v>1.064647506835629</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.02774942423927874</v>
+        <v>0.02497448181535087</v>
       </c>
       <c r="W11">
-        <v>0.2292566857643781</v>
+        <v>0.2299110171879403</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.1460496012593617</v>
+        <v>0.1314446411334256</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2331,22 +2331,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1165269293787597</v>
+        <v>0.1184269293787597</v>
       </c>
       <c r="C12">
-        <v>20.48307755878593</v>
+        <v>19.54445595578451</v>
       </c>
       <c r="D12">
-        <v>23.66917755878593</v>
+        <v>23.04996595578451</v>
       </c>
       <c r="E12">
-        <v>2.8531</v>
+        <v>3.17251</v>
       </c>
       <c r="F12">
-        <v>3.194100000000001</v>
+        <v>3.51351</v>
       </c>
       <c r="G12">
         <v>0.008</v>
@@ -2367,37 +2367,37 @@
         <v>0.099</v>
       </c>
       <c r="M12">
-        <v>0.7531687800000002</v>
+        <v>0.8284856580000001</v>
       </c>
       <c r="N12">
-        <v>-0.6541687800000002</v>
+        <v>-0.7294856580000001</v>
       </c>
       <c r="O12">
-        <v>-0.1242920682</v>
+        <v>-0.13860227502</v>
       </c>
       <c r="P12">
-        <v>-0.5298767118000002</v>
+        <v>-0.5908833829800001</v>
       </c>
       <c r="Q12">
-        <v>-0.6288767118000002</v>
+        <v>-0.6898833829800001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1039286973999619</v>
+        <v>0.1045818288314221</v>
       </c>
       <c r="T12">
-        <v>1.064647506835629</v>
+        <v>1.076609838373108</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.02497448181535087</v>
+        <v>0.0227040743775917</v>
       </c>
       <c r="W12">
-        <v>0.2299110171879403</v>
+        <v>0.2304463792617639</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.1314446411334256</v>
+        <v>0.1194951283031142</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2413,22 +2413,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1184269293787597</v>
+        <v>0.1203269293787597</v>
       </c>
       <c r="C13">
-        <v>19.54445595578451</v>
+        <v>18.63740688785221</v>
       </c>
       <c r="D13">
-        <v>23.04996595578451</v>
+        <v>22.46232688785221</v>
       </c>
       <c r="E13">
-        <v>3.17251</v>
+        <v>3.49192</v>
       </c>
       <c r="F13">
-        <v>3.51351</v>
+        <v>3.83292</v>
       </c>
       <c r="G13">
         <v>0.008</v>
@@ -2449,37 +2449,37 @@
         <v>0.099</v>
       </c>
       <c r="M13">
-        <v>0.8284856580000001</v>
+        <v>0.903802536</v>
       </c>
       <c r="N13">
-        <v>-0.7294856580000001</v>
+        <v>-0.8048025360000001</v>
       </c>
       <c r="O13">
-        <v>-0.13860227502</v>
+        <v>-0.15291248184</v>
       </c>
       <c r="P13">
-        <v>-0.5908833829800001</v>
+        <v>-0.6518900541600001</v>
       </c>
       <c r="Q13">
-        <v>-0.6898833829800001</v>
+        <v>-0.7508900541600001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1045818288314221</v>
+        <v>0.1052498041590519</v>
       </c>
       <c r="T13">
-        <v>1.076609838373108</v>
+        <v>1.088844041081893</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.0227040743775917</v>
+        <v>0.02081206817945906</v>
       </c>
       <c r="W13">
-        <v>0.2304463792617639</v>
+        <v>0.2308925143232836</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.1194951283031142</v>
+        <v>0.1095372009445214</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2495,22 +2495,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1203269293787597</v>
+        <v>0.1222269293787598</v>
       </c>
       <c r="C14">
-        <v>18.63740688785221</v>
+        <v>17.75957564243736</v>
       </c>
       <c r="D14">
-        <v>22.46232688785221</v>
+        <v>21.90390564243736</v>
       </c>
       <c r="E14">
-        <v>3.49192</v>
+        <v>3.81133</v>
       </c>
       <c r="F14">
-        <v>3.83292</v>
+        <v>4.15233</v>
       </c>
       <c r="G14">
         <v>0.008</v>
@@ -2531,37 +2531,37 @@
         <v>0.099</v>
       </c>
       <c r="M14">
-        <v>0.903802536</v>
+        <v>0.979119414</v>
       </c>
       <c r="N14">
-        <v>-0.8048025360000001</v>
+        <v>-0.880119414</v>
       </c>
       <c r="O14">
-        <v>-0.15291248184</v>
+        <v>-0.16722268866</v>
       </c>
       <c r="P14">
-        <v>-0.6518900541600001</v>
+        <v>-0.71289672534</v>
       </c>
       <c r="Q14">
-        <v>-0.7508900541600001</v>
+        <v>-0.81189672534</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1052498041590519</v>
+        <v>0.1059331352413399</v>
       </c>
       <c r="T14">
-        <v>1.088844041081893</v>
+        <v>1.101359489829961</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.02081206817945906</v>
+        <v>0.01921113985796221</v>
       </c>
       <c r="W14">
-        <v>0.2308925143232836</v>
+        <v>0.2312700132214925</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.1095372009445214</v>
+        <v>0.1011112624103274</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2577,22 +2577,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1222269293787598</v>
+        <v>0.1241269293787597</v>
       </c>
       <c r="C15">
-        <v>17.75957564243736</v>
+        <v>16.90883598288459</v>
       </c>
       <c r="D15">
-        <v>21.90390564243736</v>
+        <v>21.37257598288459</v>
       </c>
       <c r="E15">
-        <v>3.81133</v>
+        <v>4.13074</v>
       </c>
       <c r="F15">
-        <v>4.15233</v>
+        <v>4.47174</v>
       </c>
       <c r="G15">
         <v>0.008</v>
@@ -2613,37 +2613,37 @@
         <v>0.099</v>
       </c>
       <c r="M15">
-        <v>0.979119414</v>
+        <v>1.054436292</v>
       </c>
       <c r="N15">
-        <v>-0.880119414</v>
+        <v>-0.9554362920000001</v>
       </c>
       <c r="O15">
-        <v>-0.16722268866</v>
+        <v>-0.18153289548</v>
       </c>
       <c r="P15">
-        <v>-0.71289672534</v>
+        <v>-0.7739033965200001</v>
       </c>
       <c r="Q15">
-        <v>-0.81189672534</v>
+        <v>-0.87290339652</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1059331352413399</v>
+        <v>0.1066323577441462</v>
       </c>
       <c r="T15">
-        <v>1.101359489829961</v>
+        <v>1.114165995525658</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.01921113985796221</v>
+        <v>0.01783891558239348</v>
       </c>
       <c r="W15">
-        <v>0.2312700132214925</v>
+        <v>0.2315935837056716</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.1011112624103274</v>
+        <v>0.09388902938101829</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2659,22 +2659,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1241269293787597</v>
+        <v>0.1260269293787598</v>
       </c>
       <c r="C16">
-        <v>16.90883598288459</v>
+        <v>16.08326309366609</v>
       </c>
       <c r="D16">
-        <v>21.37257598288459</v>
+        <v>20.86641309366609</v>
       </c>
       <c r="E16">
-        <v>4.13074</v>
+        <v>4.450150000000001</v>
       </c>
       <c r="F16">
-        <v>4.47174</v>
+        <v>4.791150000000001</v>
       </c>
       <c r="G16">
         <v>0.008</v>
@@ -2695,37 +2695,37 @@
         <v>0.099</v>
       </c>
       <c r="M16">
-        <v>1.054436292</v>
+        <v>1.12975317</v>
       </c>
       <c r="N16">
-        <v>-0.9554362920000001</v>
+        <v>-1.03075317</v>
       </c>
       <c r="O16">
-        <v>-0.18153289548</v>
+        <v>-0.1958431023000001</v>
       </c>
       <c r="P16">
-        <v>-0.7739033965200001</v>
+        <v>-0.8349100677000003</v>
       </c>
       <c r="Q16">
-        <v>-0.87290339652</v>
+        <v>-0.9339100677000003</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1066323577441462</v>
+        <v>0.1073480325411361</v>
       </c>
       <c r="T16">
-        <v>1.114165995525658</v>
+        <v>1.127273830767137</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.01783891558239348</v>
+        <v>0.01664965454356724</v>
       </c>
       <c r="W16">
-        <v>0.2315935837056716</v>
+        <v>0.2318740114586268</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.09388902938101829</v>
+        <v>0.08762976075561701</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2741,22 +2741,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1260269293787597</v>
+        <v>0.1279269293787597</v>
       </c>
       <c r="C17">
-        <v>16.0832630936661</v>
+        <v>15.28111028107265</v>
       </c>
       <c r="D17">
-        <v>20.8664130936661</v>
+        <v>20.38367028107265</v>
       </c>
       <c r="E17">
-        <v>4.45015</v>
+        <v>4.76956</v>
       </c>
       <c r="F17">
-        <v>4.79115</v>
+        <v>5.11056</v>
       </c>
       <c r="G17">
         <v>0.008</v>
@@ -2777,37 +2777,37 @@
         <v>0.099</v>
       </c>
       <c r="M17">
-        <v>1.12975317</v>
+        <v>1.205070048</v>
       </c>
       <c r="N17">
-        <v>-1.03075317</v>
+        <v>-1.106070048</v>
       </c>
       <c r="O17">
-        <v>-0.1958431023</v>
+        <v>-0.21015330912</v>
       </c>
       <c r="P17">
-        <v>-0.8349100677000001</v>
+        <v>-0.89591673888</v>
       </c>
       <c r="Q17">
-        <v>-0.9339100677000001</v>
+        <v>-0.99491673888</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1073480325411361</v>
+        <v>0.1080807472142449</v>
       </c>
       <c r="T17">
-        <v>1.127273830767137</v>
+        <v>1.140693757323888</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.01664965454356725</v>
+        <v>0.01560905113459429</v>
       </c>
       <c r="W17">
-        <v>0.2318740114586268</v>
+        <v>0.2321193857424627</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.08762976075561701</v>
+        <v>0.08215290070839099</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2823,22 +2823,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1279269293787597</v>
+        <v>0.1298269293787597</v>
       </c>
       <c r="C18">
-        <v>15.28111028107265</v>
+        <v>14.50078883494015</v>
       </c>
       <c r="D18">
-        <v>20.38367028107265</v>
+        <v>19.92275883494015</v>
       </c>
       <c r="E18">
-        <v>4.76956</v>
+        <v>5.088970000000001</v>
       </c>
       <c r="F18">
-        <v>5.11056</v>
+        <v>5.429970000000001</v>
       </c>
       <c r="G18">
         <v>0.008</v>
@@ -2859,37 +2859,37 @@
         <v>0.099</v>
       </c>
       <c r="M18">
-        <v>1.205070048</v>
+        <v>1.280386926</v>
       </c>
       <c r="N18">
-        <v>-1.106070048</v>
+        <v>-1.181386926</v>
       </c>
       <c r="O18">
-        <v>-0.21015330912</v>
+        <v>-0.2244635159400001</v>
       </c>
       <c r="P18">
-        <v>-0.89591673888</v>
+        <v>-0.9569234100600003</v>
       </c>
       <c r="Q18">
-        <v>-0.99491673888</v>
+        <v>-1.05592341006</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1080807472142449</v>
+        <v>0.1088311176626093</v>
       </c>
       <c r="T18">
-        <v>1.140693757323888</v>
+        <v>1.154437055604899</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.01560905113459429</v>
+        <v>0.01469087165608875</v>
       </c>
       <c r="W18">
-        <v>0.2321193857424627</v>
+        <v>0.2323358924634943</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.08215290070839099</v>
+        <v>0.07732037713730922</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2905,22 +2905,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1298269293787597</v>
+        <v>0.1317269293787597</v>
       </c>
       <c r="C19">
-        <v>14.50078883494015</v>
+        <v>13.74085056213836</v>
       </c>
       <c r="D19">
-        <v>19.92275883494015</v>
+        <v>19.48223056213836</v>
       </c>
       <c r="E19">
-        <v>5.088970000000001</v>
+        <v>5.408380000000001</v>
       </c>
       <c r="F19">
-        <v>5.429970000000001</v>
+        <v>5.749380000000001</v>
       </c>
       <c r="G19">
         <v>0.008</v>
@@ -2941,37 +2941,37 @@
         <v>0.099</v>
       </c>
       <c r="M19">
-        <v>1.280386926</v>
+        <v>1.355703804</v>
       </c>
       <c r="N19">
-        <v>-1.181386926</v>
+        <v>-1.256703804</v>
       </c>
       <c r="O19">
-        <v>-0.2244635159400001</v>
+        <v>-0.2387737227600001</v>
       </c>
       <c r="P19">
-        <v>-0.9569234100600003</v>
+        <v>-1.01793008124</v>
       </c>
       <c r="Q19">
-        <v>-1.05592341006</v>
+        <v>-1.11693008124</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1088311176626093</v>
+        <v>0.1095997898292265</v>
       </c>
       <c r="T19">
-        <v>1.154437055604899</v>
+        <v>1.168515556283008</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.01469087165608875</v>
+        <v>0.01387471211963937</v>
       </c>
       <c r="W19">
-        <v>0.2323358924634943</v>
+        <v>0.232528342882189</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.07732037713730922</v>
+        <v>0.07302480062968086</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2987,22 +2987,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1317269293787597</v>
+        <v>0.1336269293787598</v>
       </c>
       <c r="C20">
-        <v>13.74085056213836</v>
+        <v>12.9999725872257</v>
       </c>
       <c r="D20">
-        <v>19.48223056213836</v>
+        <v>19.0607625872257</v>
       </c>
       <c r="E20">
-        <v>5.40838</v>
+        <v>5.727790000000001</v>
       </c>
       <c r="F20">
-        <v>5.74938</v>
+        <v>6.068790000000001</v>
       </c>
       <c r="G20">
         <v>0.008</v>
@@ -3023,37 +3023,37 @@
         <v>0.099</v>
       </c>
       <c r="M20">
-        <v>1.355703804</v>
+        <v>1.431020682</v>
       </c>
       <c r="N20">
-        <v>-1.256703804</v>
+        <v>-1.332020682</v>
       </c>
       <c r="O20">
-        <v>-0.2387737227600001</v>
+        <v>-0.25308392958</v>
       </c>
       <c r="P20">
-        <v>-1.01793008124</v>
+        <v>-1.07893675242</v>
       </c>
       <c r="Q20">
-        <v>-1.11693008124</v>
+        <v>-1.17793675242</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1095997898292265</v>
+        <v>0.1103874415555132</v>
       </c>
       <c r="T20">
-        <v>1.168515556283008</v>
+        <v>1.18294167426181</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.01387471211963937</v>
+        <v>0.01314446411334256</v>
       </c>
       <c r="W20">
-        <v>0.232528342882189</v>
+        <v>0.2327005353620738</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.07302480062968086</v>
+        <v>0.06918139007022395</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1336269293787598</v>
+        <v>0.1355269293787597</v>
       </c>
       <c r="C21">
-        <v>12.9999725872257</v>
+        <v>12.27694408421359</v>
       </c>
       <c r="D21">
-        <v>19.0607625872257</v>
+        <v>18.65714408421359</v>
       </c>
       <c r="E21">
-        <v>5.727790000000001</v>
+        <v>6.047200000000001</v>
       </c>
       <c r="F21">
-        <v>6.068790000000001</v>
+        <v>6.388200000000001</v>
       </c>
       <c r="G21">
         <v>0.008</v>
@@ -3105,37 +3105,37 @@
         <v>0.099</v>
       </c>
       <c r="M21">
-        <v>1.431020682</v>
+        <v>1.50633756</v>
       </c>
       <c r="N21">
-        <v>-1.332020682</v>
+        <v>-1.40733756</v>
       </c>
       <c r="O21">
-        <v>-0.25308392958</v>
+        <v>-0.2673941364000001</v>
       </c>
       <c r="P21">
-        <v>-1.07893675242</v>
+        <v>-1.1399434236</v>
       </c>
       <c r="Q21">
-        <v>-1.17793675242</v>
+        <v>-1.2389434236</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1103874415555132</v>
+        <v>0.1111947845749571</v>
       </c>
       <c r="T21">
-        <v>1.18294167426181</v>
+        <v>1.197728445190083</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.01314446411334256</v>
+        <v>0.01248724090767543</v>
       </c>
       <c r="W21">
-        <v>0.2327005353620738</v>
+        <v>0.2328555085939701</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.06918139007022395</v>
+        <v>0.06572232056671279</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3151,22 +3151,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1355269293787597</v>
+        <v>0.1374269293787597</v>
       </c>
       <c r="C22">
-        <v>12.27694408421359</v>
+        <v>11.57065465913243</v>
       </c>
       <c r="D22">
-        <v>18.65714408421359</v>
+        <v>18.27026465913243</v>
       </c>
       <c r="E22">
-        <v>6.047200000000001</v>
+        <v>6.366610000000001</v>
       </c>
       <c r="F22">
-        <v>6.388200000000001</v>
+        <v>6.707610000000001</v>
       </c>
       <c r="G22">
         <v>0.008</v>
@@ -3187,37 +3187,37 @@
         <v>0.099</v>
       </c>
       <c r="M22">
-        <v>1.50633756</v>
+        <v>1.581654438</v>
       </c>
       <c r="N22">
-        <v>-1.40733756</v>
+        <v>-1.482654438</v>
       </c>
       <c r="O22">
-        <v>-0.2673941364000001</v>
+        <v>-0.28170434322</v>
       </c>
       <c r="P22">
-        <v>-1.1399434236</v>
+        <v>-1.20095009478</v>
       </c>
       <c r="Q22">
-        <v>-1.2389434236</v>
+        <v>-1.29995009478</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1111947845749571</v>
+        <v>0.1120225666581844</v>
       </c>
       <c r="T22">
-        <v>1.197728445190083</v>
+        <v>1.212889564749451</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.01248724090767543</v>
+        <v>0.01189261038826232</v>
       </c>
       <c r="W22">
-        <v>0.2328555085939701</v>
+        <v>0.2329957224704478</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.06572232056671279</v>
+        <v>0.06259268625401215</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3233,22 +3233,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1374269293787597</v>
+        <v>0.1393269293787597</v>
       </c>
       <c r="C23">
-        <v>11.57065465913244</v>
+        <v>10.88008414864704</v>
       </c>
       <c r="D23">
-        <v>18.27026465913244</v>
+        <v>17.89910414864704</v>
       </c>
       <c r="E23">
-        <v>6.36661</v>
+        <v>6.68602</v>
       </c>
       <c r="F23">
-        <v>6.70761</v>
+        <v>7.02702</v>
       </c>
       <c r="G23">
         <v>0.008</v>
@@ -3269,37 +3269,37 @@
         <v>0.099</v>
       </c>
       <c r="M23">
-        <v>1.581654438</v>
+        <v>1.656971316</v>
       </c>
       <c r="N23">
-        <v>-1.482654438</v>
+        <v>-1.557971316</v>
       </c>
       <c r="O23">
-        <v>-0.28170434322</v>
+        <v>-0.29601455004</v>
       </c>
       <c r="P23">
-        <v>-1.20095009478</v>
+        <v>-1.26195676596</v>
       </c>
       <c r="Q23">
-        <v>-1.29995009478</v>
+        <v>-1.36095676596</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1120225666581844</v>
+        <v>0.112871573923033</v>
       </c>
       <c r="T23">
-        <v>1.212889564749451</v>
+        <v>1.228439430964188</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.01189261038826232</v>
+        <v>0.01135203718879585</v>
       </c>
       <c r="W23">
-        <v>0.2329957224704478</v>
+        <v>0.2331231896308819</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.06259268625401215</v>
+        <v>0.05974756415155713</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3315,22 +3315,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1393269293787597</v>
+        <v>0.1412269293787597</v>
       </c>
       <c r="C24">
-        <v>10.88008414864704</v>
+        <v>10.20429363736131</v>
       </c>
       <c r="D24">
-        <v>17.89910414864704</v>
+        <v>17.54272363736131</v>
       </c>
       <c r="E24">
-        <v>6.68602</v>
+        <v>7.00543</v>
       </c>
       <c r="F24">
-        <v>7.02702</v>
+        <v>7.346430000000001</v>
       </c>
       <c r="G24">
         <v>0.008</v>
@@ -3351,37 +3351,37 @@
         <v>0.099</v>
       </c>
       <c r="M24">
-        <v>1.656971316</v>
+        <v>1.732288194</v>
       </c>
       <c r="N24">
-        <v>-1.557971316</v>
+        <v>-1.633288194</v>
       </c>
       <c r="O24">
-        <v>-0.29601455004</v>
+        <v>-0.3103247568600001</v>
       </c>
       <c r="P24">
-        <v>-1.26195676596</v>
+        <v>-1.32296343714</v>
       </c>
       <c r="Q24">
-        <v>-1.36095676596</v>
+        <v>-1.42196343714</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.112871573923033</v>
+        <v>0.1137426333246308</v>
       </c>
       <c r="T24">
-        <v>1.228439430964188</v>
+        <v>1.244393189807878</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.01135203718879585</v>
+        <v>0.01085847035450038</v>
       </c>
       <c r="W24">
-        <v>0.2331231896308819</v>
+        <v>0.2332395726904088</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.05974756415155713</v>
+        <v>0.0571498439710546</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3397,22 +3397,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1412269293787597</v>
+        <v>0.1431269293787598</v>
       </c>
       <c r="C25">
-        <v>10.20429363736131</v>
+        <v>9.542417527275026</v>
       </c>
       <c r="D25">
-        <v>17.54272363736131</v>
+        <v>17.20025752727503</v>
       </c>
       <c r="E25">
-        <v>7.00543</v>
+        <v>7.324840000000001</v>
       </c>
       <c r="F25">
-        <v>7.346430000000001</v>
+        <v>7.665840000000001</v>
       </c>
       <c r="G25">
         <v>0.008</v>
@@ -3433,37 +3433,37 @@
         <v>0.099</v>
       </c>
       <c r="M25">
-        <v>1.732288194</v>
+        <v>1.807605072</v>
       </c>
       <c r="N25">
-        <v>-1.633288194</v>
+        <v>-1.708605072</v>
       </c>
       <c r="O25">
-        <v>-0.3103247568600001</v>
+        <v>-0.3246349636800001</v>
       </c>
       <c r="P25">
-        <v>-1.32296343714</v>
+        <v>-1.38397010832</v>
       </c>
       <c r="Q25">
-        <v>-1.42196343714</v>
+        <v>-1.48297010832</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1137426333246308</v>
+        <v>0.1146366153420602</v>
       </c>
       <c r="T25">
-        <v>1.244393189807878</v>
+        <v>1.260766784410614</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.01085847035450038</v>
+        <v>0.01040603408972953</v>
       </c>
       <c r="W25">
-        <v>0.2332395726904088</v>
+        <v>0.2333462571616418</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.0571498439710546</v>
+        <v>0.05476860047226062</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3479,22 +3479,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1431269293787598</v>
+        <v>0.1450269293787597</v>
       </c>
       <c r="C26">
-        <v>9.542417527275028</v>
+        <v>8.893656518366168</v>
       </c>
       <c r="D26">
-        <v>17.20025752727503</v>
+        <v>16.87090651836617</v>
       </c>
       <c r="E26">
-        <v>7.32484</v>
+        <v>7.64425</v>
       </c>
       <c r="F26">
-        <v>7.66584</v>
+        <v>7.985250000000001</v>
       </c>
       <c r="G26">
         <v>0.008</v>
@@ -3515,37 +3515,37 @@
         <v>0.099</v>
       </c>
       <c r="M26">
-        <v>1.807605072</v>
+        <v>1.88292195</v>
       </c>
       <c r="N26">
-        <v>-1.708605072</v>
+        <v>-1.78392195</v>
       </c>
       <c r="O26">
-        <v>-0.32463496368</v>
+        <v>-0.3389451705000001</v>
       </c>
       <c r="P26">
-        <v>-1.38397010832</v>
+        <v>-1.4449767795</v>
       </c>
       <c r="Q26">
-        <v>-1.48297010832</v>
+        <v>-1.5439767795</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1146366153420602</v>
+        <v>0.1155544368799543</v>
       </c>
       <c r="T26">
-        <v>1.260766784410614</v>
+        <v>1.277577008202755</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.01040603408972953</v>
+        <v>0.009989792726140348</v>
       </c>
       <c r="W26">
-        <v>0.2333462571616418</v>
+        <v>0.2334444068751761</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.05476860047226062</v>
+        <v>0.05257785645337021</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3561,22 +3561,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1450269293787597</v>
+        <v>0.1469269293787597</v>
       </c>
       <c r="C27">
-        <v>8.893656518366168</v>
+        <v>8.257271380469538</v>
       </c>
       <c r="D27">
-        <v>16.87090651836617</v>
+        <v>16.55393138046954</v>
       </c>
       <c r="E27">
-        <v>7.64425</v>
+        <v>7.96366</v>
       </c>
       <c r="F27">
-        <v>7.985250000000001</v>
+        <v>8.30466</v>
       </c>
       <c r="G27">
         <v>0.008</v>
@@ -3597,37 +3597,37 @@
         <v>0.099</v>
       </c>
       <c r="M27">
-        <v>1.88292195</v>
+        <v>1.958238828</v>
       </c>
       <c r="N27">
-        <v>-1.78392195</v>
+        <v>-1.859238828</v>
       </c>
       <c r="O27">
-        <v>-0.3389451705000001</v>
+        <v>-0.35325537732</v>
       </c>
       <c r="P27">
-        <v>-1.4449767795</v>
+        <v>-1.50598345068</v>
       </c>
       <c r="Q27">
-        <v>-1.5439767795</v>
+        <v>-1.60498345068</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1155544368799543</v>
+        <v>0.1164970644053591</v>
       </c>
       <c r="T27">
-        <v>1.277577008202755</v>
+        <v>1.294841562367657</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.009989792726140348</v>
+        <v>0.009605569928981105</v>
       </c>
       <c r="W27">
-        <v>0.2334444068751761</v>
+        <v>0.2335350066107463</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.05257785645337021</v>
+        <v>0.05055563120516371</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3643,22 +3643,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1469269293787597</v>
+        <v>0.1488269293787597</v>
       </c>
       <c r="C28">
-        <v>8.257271380469538</v>
+        <v>7.632577414301201</v>
       </c>
       <c r="D28">
-        <v>16.55393138046954</v>
+        <v>16.2486474143012</v>
       </c>
       <c r="E28">
-        <v>7.96366</v>
+        <v>8.283070000000002</v>
       </c>
       <c r="F28">
-        <v>8.30466</v>
+        <v>8.624070000000001</v>
       </c>
       <c r="G28">
         <v>0.008</v>
@@ -3679,37 +3679,37 @@
         <v>0.099</v>
       </c>
       <c r="M28">
-        <v>1.958238828</v>
+        <v>2.033555706</v>
       </c>
       <c r="N28">
-        <v>-1.859238828</v>
+        <v>-1.934555706</v>
       </c>
       <c r="O28">
-        <v>-0.35325537732</v>
+        <v>-0.3675655841400001</v>
       </c>
       <c r="P28">
-        <v>-1.50598345068</v>
+        <v>-1.56699012186</v>
       </c>
       <c r="Q28">
-        <v>-1.60498345068</v>
+        <v>-1.66599012186</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1164970644053591</v>
+        <v>0.1174655173424188</v>
       </c>
       <c r="T28">
-        <v>1.294841562367657</v>
+        <v>1.312579118016529</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.009605569928981105</v>
+        <v>0.009249808079759581</v>
       </c>
       <c r="W28">
-        <v>0.2335350066107463</v>
+        <v>0.2336188952547927</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.05055563120516371</v>
+        <v>0.04868320041978724</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3725,22 +3725,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1488269293787597</v>
+        <v>0.1507269293787598</v>
       </c>
       <c r="C29">
-        <v>7.632577414301201</v>
+        <v>7.018939514276315</v>
       </c>
       <c r="D29">
-        <v>16.2486474143012</v>
+        <v>15.95441951427632</v>
       </c>
       <c r="E29">
-        <v>8.283070000000002</v>
+        <v>8.602480000000002</v>
       </c>
       <c r="F29">
-        <v>8.624070000000001</v>
+        <v>8.943480000000001</v>
       </c>
       <c r="G29">
         <v>0.008</v>
@@ -3761,37 +3761,37 @@
         <v>0.099</v>
       </c>
       <c r="M29">
-        <v>2.033555706</v>
+        <v>2.108872584</v>
       </c>
       <c r="N29">
-        <v>-1.934555706</v>
+        <v>-2.009872584</v>
       </c>
       <c r="O29">
-        <v>-0.3675655841400001</v>
+        <v>-0.38187579096</v>
       </c>
       <c r="P29">
-        <v>-1.56699012186</v>
+        <v>-1.62799679304</v>
       </c>
       <c r="Q29">
-        <v>-1.66599012186</v>
+        <v>-1.72699679304</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1174655173424188</v>
+        <v>0.1184608717499524</v>
       </c>
       <c r="T29">
-        <v>1.312579118016529</v>
+        <v>1.330809383544536</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.009249808079759581</v>
+        <v>0.008919457791196739</v>
       </c>
       <c r="W29">
-        <v>0.2336188952547927</v>
+        <v>0.2336967918528358</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.04868320041978724</v>
+        <v>0.0469445146905092</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3807,22 +3807,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1507269293787598</v>
+        <v>0.1526269293787597</v>
       </c>
       <c r="C30">
-        <v>7.018939514276315</v>
+        <v>6.415767758196562</v>
       </c>
       <c r="D30">
-        <v>15.95441951427632</v>
+        <v>15.67065775819657</v>
       </c>
       <c r="E30">
-        <v>8.602480000000002</v>
+        <v>8.921890000000003</v>
       </c>
       <c r="F30">
-        <v>8.943480000000001</v>
+        <v>9.262890000000002</v>
       </c>
       <c r="G30">
         <v>0.008</v>
@@ -3843,37 +3843,37 @@
         <v>0.099</v>
       </c>
       <c r="M30">
-        <v>2.108872584</v>
+        <v>2.184189462</v>
       </c>
       <c r="N30">
-        <v>-2.009872584</v>
+        <v>-2.085189462</v>
       </c>
       <c r="O30">
-        <v>-0.38187579096</v>
+        <v>-0.39618599778</v>
       </c>
       <c r="P30">
-        <v>-1.62799679304</v>
+        <v>-1.68900346422</v>
       </c>
       <c r="Q30">
-        <v>-1.72699679304</v>
+        <v>-1.78800346422</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1184608717499524</v>
+        <v>0.1194842643098109</v>
       </c>
       <c r="T30">
-        <v>1.330809383544536</v>
+        <v>1.349553177678966</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.008919457791196739</v>
+        <v>0.008611890281155471</v>
       </c>
       <c r="W30">
-        <v>0.2336967918528358</v>
+        <v>0.2337693162717036</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.0469445146905092</v>
+        <v>0.04532573832187103</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3889,22 +3889,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1526269293787597</v>
+        <v>0.1545269293787597</v>
       </c>
       <c r="C31">
-        <v>6.415767758196564</v>
+        <v>5.822513459358211</v>
       </c>
       <c r="D31">
-        <v>15.67065775819657</v>
+        <v>15.39681345935821</v>
       </c>
       <c r="E31">
-        <v>8.921890000000001</v>
+        <v>9.241300000000001</v>
       </c>
       <c r="F31">
-        <v>9.262890000000001</v>
+        <v>9.5823</v>
       </c>
       <c r="G31">
         <v>0.008</v>
@@ -3925,37 +3925,37 @@
         <v>0.099</v>
       </c>
       <c r="M31">
-        <v>2.184189462</v>
+        <v>2.25950634</v>
       </c>
       <c r="N31">
-        <v>-2.085189462</v>
+        <v>-2.16050634</v>
       </c>
       <c r="O31">
-        <v>-0.39618599778</v>
+        <v>-0.4104962046</v>
       </c>
       <c r="P31">
-        <v>-1.68900346422</v>
+        <v>-1.7500101354</v>
       </c>
       <c r="Q31">
-        <v>-1.78800346422</v>
+        <v>-1.8490101354</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1194842643098109</v>
+        <v>0.1205368966570939</v>
       </c>
       <c r="T31">
-        <v>1.349553177678966</v>
+        <v>1.368832508788666</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.008611890281155471</v>
+        <v>0.008324827271783623</v>
       </c>
       <c r="W31">
-        <v>0.2337693162717036</v>
+        <v>0.2338370057293134</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.04532573832187103</v>
+        <v>0.04381488037780867</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3971,22 +3971,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1545269293787597</v>
+        <v>0.1564269293787597</v>
       </c>
       <c r="C32">
-        <v>5.822513459358211</v>
+        <v>5.238665625486654</v>
       </c>
       <c r="D32">
-        <v>15.39681345935821</v>
+        <v>15.13237562548666</v>
       </c>
       <c r="E32">
-        <v>9.241300000000001</v>
+        <v>9.560710000000002</v>
       </c>
       <c r="F32">
-        <v>9.5823</v>
+        <v>9.901710000000001</v>
       </c>
       <c r="G32">
         <v>0.008</v>
@@ -4007,37 +4007,37 @@
         <v>0.099</v>
       </c>
       <c r="M32">
-        <v>2.25950634</v>
+        <v>2.334823218</v>
       </c>
       <c r="N32">
-        <v>-2.16050634</v>
+        <v>-2.235823218</v>
       </c>
       <c r="O32">
-        <v>-0.4104962046</v>
+        <v>-0.42480641142</v>
       </c>
       <c r="P32">
-        <v>-1.7500101354</v>
+        <v>-1.81101680658</v>
       </c>
       <c r="Q32">
-        <v>-1.8490101354</v>
+        <v>-1.91001680658</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1205368966570939</v>
+        <v>0.1216200400869068</v>
       </c>
       <c r="T32">
-        <v>1.368832508788666</v>
+        <v>1.388670661089951</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.008324827271783623</v>
+        <v>0.008056284456564795</v>
       </c>
       <c r="W32">
-        <v>0.2338370057293134</v>
+        <v>0.233900328125142</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.04381488037780867</v>
+        <v>0.04240149713981478</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4053,22 +4053,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1564269293787597</v>
+        <v>0.1583269293787598</v>
       </c>
       <c r="C33">
-        <v>5.238665625486654</v>
+        <v>4.663747776413047</v>
       </c>
       <c r="D33">
-        <v>15.13237562548666</v>
+        <v>14.87686777641305</v>
       </c>
       <c r="E33">
-        <v>9.560710000000002</v>
+        <v>9.880120000000002</v>
       </c>
       <c r="F33">
-        <v>9.901710000000001</v>
+        <v>10.22112</v>
       </c>
       <c r="G33">
         <v>0.008</v>
@@ -4089,37 +4089,37 @@
         <v>0.099</v>
       </c>
       <c r="M33">
-        <v>2.334823218</v>
+        <v>2.410140096</v>
       </c>
       <c r="N33">
-        <v>-2.235823218</v>
+        <v>-2.311140096</v>
       </c>
       <c r="O33">
-        <v>-0.42480641142</v>
+        <v>-0.43911661824</v>
       </c>
       <c r="P33">
-        <v>-1.81101680658</v>
+        <v>-1.87202347776</v>
       </c>
       <c r="Q33">
-        <v>-1.91001680658</v>
+        <v>-1.97102347776</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1216200400869068</v>
+        <v>0.1227350406764202</v>
       </c>
       <c r="T33">
-        <v>1.388670661089951</v>
+        <v>1.409092288458921</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.008056284456564795</v>
+        <v>0.007804525567297146</v>
       </c>
       <c r="W33">
-        <v>0.233900328125142</v>
+        <v>0.2339596928712313</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.04240149713981478</v>
+        <v>0.0410764503541956</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1583269293787598</v>
+        <v>0.1602269293787597</v>
       </c>
       <c r="C34">
-        <v>4.663747776413047</v>
+        <v>4.09731507879593</v>
       </c>
       <c r="D34">
-        <v>14.87686777641305</v>
+        <v>14.62984507879593</v>
       </c>
       <c r="E34">
-        <v>9.880120000000002</v>
+        <v>10.19953</v>
       </c>
       <c r="F34">
-        <v>10.22112</v>
+        <v>10.54053</v>
       </c>
       <c r="G34">
         <v>0.008</v>
@@ -4171,37 +4171,37 @@
         <v>0.099</v>
       </c>
       <c r="M34">
-        <v>2.410140096</v>
+        <v>2.485456974000001</v>
       </c>
       <c r="N34">
-        <v>-2.311140096</v>
+        <v>-2.386456974000001</v>
       </c>
       <c r="O34">
-        <v>-0.43911661824</v>
+        <v>-0.4534268250600001</v>
       </c>
       <c r="P34">
-        <v>-1.87202347776</v>
+        <v>-1.93303014894</v>
       </c>
       <c r="Q34">
-        <v>-1.97102347776</v>
+        <v>-2.032030148940001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1227350406764202</v>
+        <v>0.1238833248656205</v>
       </c>
       <c r="T34">
-        <v>1.409092288458921</v>
+        <v>1.430123516644875</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.007804525567297146</v>
+        <v>0.007568024792530565</v>
       </c>
       <c r="W34">
-        <v>0.2339596928712313</v>
+        <v>0.2340154597539213</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.0410764503541956</v>
+        <v>0.03983170943437142</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4217,22 +4217,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1602269293787597</v>
+        <v>0.1621269293787597</v>
       </c>
       <c r="C35">
-        <v>4.09731507879593</v>
+        <v>3.538951761639186</v>
       </c>
       <c r="D35">
-        <v>14.62984507879593</v>
+        <v>14.39089176163919</v>
       </c>
       <c r="E35">
-        <v>10.19953</v>
+        <v>10.51894</v>
       </c>
       <c r="F35">
-        <v>10.54053</v>
+        <v>10.85994</v>
       </c>
       <c r="G35">
         <v>0.008</v>
@@ -4253,37 +4253,37 @@
         <v>0.099</v>
       </c>
       <c r="M35">
-        <v>2.485456974000001</v>
+        <v>2.560773852000001</v>
       </c>
       <c r="N35">
-        <v>-2.386456974000001</v>
+        <v>-2.461773852</v>
       </c>
       <c r="O35">
-        <v>-0.4534268250600001</v>
+        <v>-0.46773703188</v>
       </c>
       <c r="P35">
-        <v>-1.93303014894</v>
+        <v>-1.99403682012</v>
       </c>
       <c r="Q35">
-        <v>-2.032030148940001</v>
+        <v>-2.09303682012</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1238833248656205</v>
+        <v>0.1250664055454026</v>
       </c>
       <c r="T35">
-        <v>1.430123516644875</v>
+        <v>1.451792054775858</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.007568024792530565</v>
+        <v>0.007345435828044373</v>
       </c>
       <c r="W35">
-        <v>0.2340154597539213</v>
+        <v>0.2340679462317471</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.03983170943437142</v>
+        <v>0.03866018856865472</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4299,22 +4299,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1621269293787597</v>
+        <v>0.1640269293787597</v>
       </c>
       <c r="C36">
-        <v>3.538951761639186</v>
+        <v>2.988268781018018</v>
       </c>
       <c r="D36">
-        <v>14.39089176163919</v>
+        <v>14.15961878101802</v>
       </c>
       <c r="E36">
-        <v>10.51894</v>
+        <v>10.83835</v>
       </c>
       <c r="F36">
-        <v>10.85994</v>
+        <v>11.17935</v>
       </c>
       <c r="G36">
         <v>0.008</v>
@@ -4335,37 +4335,37 @@
         <v>0.099</v>
       </c>
       <c r="M36">
-        <v>2.560773852000001</v>
+        <v>2.63609073</v>
       </c>
       <c r="N36">
-        <v>-2.461773852</v>
+        <v>-2.53709073</v>
       </c>
       <c r="O36">
-        <v>-0.46773703188</v>
+        <v>-0.4820472387</v>
       </c>
       <c r="P36">
-        <v>-1.99403682012</v>
+        <v>-2.0550434913</v>
       </c>
       <c r="Q36">
-        <v>-2.09303682012</v>
+        <v>-2.1540434913</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1250664055454026</v>
+        <v>0.1262858887076395</v>
       </c>
       <c r="T36">
-        <v>1.451792054775858</v>
+        <v>1.474127317157025</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.007345435828044373</v>
+        <v>0.007135566232957391</v>
       </c>
       <c r="W36">
-        <v>0.2340679462317471</v>
+        <v>0.2341174334822687</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.03866018856865472</v>
+        <v>0.0375556117524074</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4381,22 +4381,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1640269293787597</v>
+        <v>0.1659269293787597</v>
       </c>
       <c r="C37">
-        <v>2.988268781018018</v>
+        <v>2.444901706421458</v>
       </c>
       <c r="D37">
-        <v>14.15961878101802</v>
+        <v>13.93566170642146</v>
       </c>
       <c r="E37">
-        <v>10.83835</v>
+        <v>11.15776</v>
       </c>
       <c r="F37">
-        <v>11.17935</v>
+        <v>11.49876</v>
       </c>
       <c r="G37">
         <v>0.008</v>
@@ -4417,37 +4417,37 @@
         <v>0.099</v>
       </c>
       <c r="M37">
-        <v>2.63609073</v>
+        <v>2.711407608000001</v>
       </c>
       <c r="N37">
-        <v>-2.53709073</v>
+        <v>-2.612407608000001</v>
       </c>
       <c r="O37">
-        <v>-0.4820472387</v>
+        <v>-0.4963574455200002</v>
       </c>
       <c r="P37">
-        <v>-2.0550434913</v>
+        <v>-2.116050162480001</v>
       </c>
       <c r="Q37">
-        <v>-2.1540434913</v>
+        <v>-2.215050162480001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1262858887076395</v>
+        <v>0.1275434807186964</v>
       </c>
       <c r="T37">
-        <v>1.474127317157025</v>
+        <v>1.497160556487604</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.007135566232957391</v>
+        <v>0.006937356059819684</v>
       </c>
       <c r="W37">
-        <v>0.2341174334822687</v>
+        <v>0.2341641714410945</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.0375556117524074</v>
+        <v>0.03651240031484049</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4463,22 +4463,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1659269293787597</v>
+        <v>0.1678269293787598</v>
       </c>
       <c r="C38">
-        <v>2.44490170642146</v>
+        <v>1.908508804557099</v>
       </c>
       <c r="D38">
-        <v>13.93566170642146</v>
+        <v>13.7186788045571</v>
       </c>
       <c r="E38">
-        <v>11.15776</v>
+        <v>11.47717</v>
       </c>
       <c r="F38">
-        <v>11.49876</v>
+        <v>11.81817</v>
       </c>
       <c r="G38">
         <v>0.008</v>
@@ -4499,37 +4499,37 @@
         <v>0.099</v>
       </c>
       <c r="M38">
-        <v>2.711407608</v>
+        <v>2.786724486</v>
       </c>
       <c r="N38">
-        <v>-2.612407608</v>
+        <v>-2.687724486</v>
       </c>
       <c r="O38">
-        <v>-0.4963574455200001</v>
+        <v>-0.51066765234</v>
       </c>
       <c r="P38">
-        <v>-2.11605016248</v>
+        <v>-2.17705683366</v>
       </c>
       <c r="Q38">
-        <v>-2.21505016248</v>
+        <v>-2.27605683366</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1275434807186964</v>
+        <v>0.1288409962856599</v>
       </c>
       <c r="T38">
-        <v>1.497160556487603</v>
+        <v>1.520925009765185</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.006937356059819684</v>
+        <v>0.00674985995009483</v>
       </c>
       <c r="W38">
-        <v>0.2341641714410945</v>
+        <v>0.2342083830237676</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.03651240031484049</v>
+        <v>0.03552557868470974</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4545,22 +4545,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1678269293787598</v>
+        <v>0.1697269293787597</v>
       </c>
       <c r="C39">
-        <v>1.908508804557099</v>
+        <v>1.378769299425938</v>
       </c>
       <c r="D39">
-        <v>13.7186788045571</v>
+        <v>13.50834929942594</v>
       </c>
       <c r="E39">
-        <v>11.47717</v>
+        <v>11.79658</v>
       </c>
       <c r="F39">
-        <v>11.81817</v>
+        <v>12.13758</v>
       </c>
       <c r="G39">
         <v>0.008</v>
@@ -4581,37 +4581,37 @@
         <v>0.099</v>
       </c>
       <c r="M39">
-        <v>2.786724486</v>
+        <v>2.862041364</v>
       </c>
       <c r="N39">
-        <v>-2.687724486</v>
+        <v>-2.763041364</v>
       </c>
       <c r="O39">
-        <v>-0.51066765234</v>
+        <v>-0.5249778591600001</v>
       </c>
       <c r="P39">
-        <v>-2.17705683366</v>
+        <v>-2.23806350484</v>
       </c>
       <c r="Q39">
-        <v>-2.27605683366</v>
+        <v>-2.337063504840001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1288409962856599</v>
+        <v>0.1301803671934931</v>
       </c>
       <c r="T39">
-        <v>1.520925009765185</v>
+        <v>1.545456058309784</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.00674985995009483</v>
+        <v>0.006572232056671281</v>
       </c>
       <c r="W39">
-        <v>0.2342083830237676</v>
+        <v>0.2342502676810369</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.03552557868470974</v>
+        <v>0.03459069503511203</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4627,22 +4627,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1697269293787597</v>
+        <v>0.1716269293787597</v>
       </c>
       <c r="C40">
-        <v>1.378769299425938</v>
+        <v>0.8553817900356346</v>
       </c>
       <c r="D40">
-        <v>13.50834929942594</v>
+        <v>13.30437179003564</v>
       </c>
       <c r="E40">
-        <v>11.79658</v>
+        <v>12.11599</v>
       </c>
       <c r="F40">
-        <v>12.13758</v>
+        <v>12.45699</v>
       </c>
       <c r="G40">
         <v>0.008</v>
@@ -4663,37 +4663,37 @@
         <v>0.099</v>
       </c>
       <c r="M40">
-        <v>2.862041364</v>
+        <v>2.937358242</v>
       </c>
       <c r="N40">
-        <v>-2.763041364</v>
+        <v>-2.838358242</v>
       </c>
       <c r="O40">
-        <v>-0.5249778591600001</v>
+        <v>-0.53928806598</v>
       </c>
       <c r="P40">
-        <v>-2.23806350484</v>
+        <v>-2.29907017602</v>
       </c>
       <c r="Q40">
-        <v>-2.337063504840001</v>
+        <v>-2.39807017602</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1301803671934931</v>
+        <v>0.1315636519015831</v>
       </c>
       <c r="T40">
-        <v>1.545456058309784</v>
+        <v>1.570791403527978</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.006572232056671281</v>
+        <v>0.006403713285987402</v>
       </c>
       <c r="W40">
-        <v>0.2342502676810369</v>
+        <v>0.2342900044071642</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.03459069503511203</v>
+        <v>0.03370375413677584</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4709,22 +4709,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1716269293787597</v>
+        <v>0.1735269293787597</v>
       </c>
       <c r="C41">
-        <v>0.8553817900356346</v>
+        <v>0.3380628093373836</v>
       </c>
       <c r="D41">
-        <v>13.30437179003564</v>
+        <v>13.10646280933739</v>
       </c>
       <c r="E41">
-        <v>12.11599</v>
+        <v>12.4354</v>
       </c>
       <c r="F41">
-        <v>12.45699</v>
+        <v>12.7764</v>
       </c>
       <c r="G41">
         <v>0.008</v>
@@ -4745,37 +4745,37 @@
         <v>0.099</v>
       </c>
       <c r="M41">
-        <v>2.937358242</v>
+        <v>3.012675120000001</v>
       </c>
       <c r="N41">
-        <v>-2.838358242</v>
+        <v>-2.913675120000001</v>
       </c>
       <c r="O41">
-        <v>-0.53928806598</v>
+        <v>-0.5535982728000001</v>
       </c>
       <c r="P41">
-        <v>-2.29907017602</v>
+        <v>-2.360076847200001</v>
       </c>
       <c r="Q41">
-        <v>-2.39807017602</v>
+        <v>-2.459076847200001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1315636519015831</v>
+        <v>0.1329930460999428</v>
       </c>
       <c r="T41">
-        <v>1.570791403527978</v>
+        <v>1.596971260253444</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.006403713285987402</v>
+        <v>0.006243620453837717</v>
       </c>
       <c r="W41">
-        <v>0.2342900044071642</v>
+        <v>0.2343277542969851</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.03370375413677584</v>
+        <v>0.03286116028335651</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4791,22 +4791,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1735269293787597</v>
+        <v>0.1754269293787598</v>
       </c>
       <c r="C42">
-        <v>0.3380628093373836</v>
+        <v>-0.1734544901032944</v>
       </c>
       <c r="D42">
-        <v>13.10646280933739</v>
+        <v>12.91435550989671</v>
       </c>
       <c r="E42">
-        <v>12.4354</v>
+        <v>12.75481</v>
       </c>
       <c r="F42">
-        <v>12.7764</v>
+        <v>13.09581</v>
       </c>
       <c r="G42">
         <v>0.008</v>
@@ -4827,37 +4827,37 @@
         <v>0.099</v>
       </c>
       <c r="M42">
-        <v>3.012675120000001</v>
+        <v>3.087991998000001</v>
       </c>
       <c r="N42">
-        <v>-2.913675120000001</v>
+        <v>-2.988991998</v>
       </c>
       <c r="O42">
-        <v>-0.5535982728000001</v>
+        <v>-0.5679084796200001</v>
       </c>
       <c r="P42">
-        <v>-2.360076847200001</v>
+        <v>-2.42108351838</v>
       </c>
       <c r="Q42">
-        <v>-2.459076847200001</v>
+        <v>-2.52008351838</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1329930460999428</v>
+        <v>0.1344708943389249</v>
       </c>
       <c r="T42">
-        <v>1.596971260253444</v>
+        <v>1.624038569749265</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.006243620453837717</v>
+        <v>0.006091337028134357</v>
       </c>
       <c r="W42">
-        <v>0.2343277542969851</v>
+        <v>0.2343636627287659</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.03286116028335651</v>
+        <v>0.03205966856912823</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4873,22 +4873,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1754269293787598</v>
+        <v>0.1773269293787597</v>
       </c>
       <c r="C43">
-        <v>-0.1734544901032944</v>
+        <v>-0.6794215365172889</v>
       </c>
       <c r="D43">
-        <v>12.91435550989671</v>
+        <v>12.72779846348271</v>
       </c>
       <c r="E43">
-        <v>12.75481</v>
+        <v>13.07422</v>
       </c>
       <c r="F43">
-        <v>13.09581</v>
+        <v>13.41522</v>
       </c>
       <c r="G43">
         <v>0.008</v>
@@ -4909,37 +4909,37 @@
         <v>0.099</v>
       </c>
       <c r="M43">
-        <v>3.087991998000001</v>
+        <v>3.163308876</v>
       </c>
       <c r="N43">
-        <v>-2.988991998</v>
+        <v>-3.064308876</v>
       </c>
       <c r="O43">
-        <v>-0.5679084796200001</v>
+        <v>-0.5822186864400001</v>
       </c>
       <c r="P43">
-        <v>-2.42108351838</v>
+        <v>-2.48209018956</v>
       </c>
       <c r="Q43">
-        <v>-2.52008351838</v>
+        <v>-2.58109018956</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1344708943389249</v>
+        <v>0.1359997028620099</v>
       </c>
       <c r="T43">
-        <v>1.624038569749265</v>
+        <v>1.652039234744942</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.006091337028134357</v>
+        <v>0.00594630519413116</v>
       </c>
       <c r="W43">
-        <v>0.2343636627287659</v>
+        <v>0.2343978612352239</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.03205966856912823</v>
+        <v>0.03129634312700613</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4955,22 +4955,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1773269293787597</v>
+        <v>0.1792269293787598</v>
       </c>
       <c r="C44">
-        <v>-0.6794215365172871</v>
+        <v>-1.180075436779504</v>
       </c>
       <c r="D44">
-        <v>12.72779846348271</v>
+        <v>12.5465545632205</v>
       </c>
       <c r="E44">
-        <v>13.07422</v>
+        <v>13.39363</v>
       </c>
       <c r="F44">
-        <v>13.41522</v>
+        <v>13.73463</v>
       </c>
       <c r="G44">
         <v>0.008</v>
@@ -4991,37 +4991,37 @@
         <v>0.099</v>
       </c>
       <c r="M44">
-        <v>3.163308876</v>
+        <v>3.238625754000001</v>
       </c>
       <c r="N44">
-        <v>-3.064308876</v>
+        <v>-3.139625754</v>
       </c>
       <c r="O44">
-        <v>-0.58221868644</v>
+        <v>-0.59652889326</v>
       </c>
       <c r="P44">
-        <v>-2.48209018956</v>
+        <v>-2.54309686074</v>
       </c>
       <c r="Q44">
-        <v>-2.58109018956</v>
+        <v>-2.642096860740001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1359997028620098</v>
+        <v>0.1375821537894135</v>
       </c>
       <c r="T44">
-        <v>1.652039234744942</v>
+        <v>1.681022379214151</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.00594630519413116</v>
+        <v>0.005808019026825783</v>
       </c>
       <c r="W44">
-        <v>0.2343978612352239</v>
+        <v>0.2344304691134745</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.03129634312700613</v>
+        <v>0.03056852119381992</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5037,22 +5037,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1792269293787598</v>
+        <v>0.1811269293787597</v>
       </c>
       <c r="C45">
-        <v>-1.180075436779504</v>
+        <v>-1.675639981773266</v>
       </c>
       <c r="D45">
-        <v>12.5465545632205</v>
+        <v>12.37040001822674</v>
       </c>
       <c r="E45">
-        <v>13.39363</v>
+        <v>13.71304</v>
       </c>
       <c r="F45">
-        <v>13.73463</v>
+        <v>14.05404</v>
       </c>
       <c r="G45">
         <v>0.008</v>
@@ -5073,37 +5073,37 @@
         <v>0.099</v>
       </c>
       <c r="M45">
-        <v>3.238625754000001</v>
+        <v>3.313942632</v>
       </c>
       <c r="N45">
-        <v>-3.139625754</v>
+        <v>-3.214942632</v>
       </c>
       <c r="O45">
-        <v>-0.59652889326</v>
+        <v>-0.61083910008</v>
       </c>
       <c r="P45">
-        <v>-2.54309686074</v>
+        <v>-2.60410353192</v>
       </c>
       <c r="Q45">
-        <v>-2.642096860740001</v>
+        <v>-2.70310353192</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1375821537894135</v>
+        <v>0.1392211208213673</v>
       </c>
       <c r="T45">
-        <v>1.681022379214151</v>
+        <v>1.711040635985833</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.005808019026825783</v>
+        <v>0.005676018594397925</v>
       </c>
       <c r="W45">
-        <v>0.2344304691134745</v>
+        <v>0.234461594815441</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.03056852119381992</v>
+        <v>0.02987378207577862</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5119,22 +5119,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1811269293787597</v>
+        <v>0.1830269293787598</v>
       </c>
       <c r="C46">
-        <v>-1.675639981773266</v>
+        <v>-2.166326568235085</v>
       </c>
       <c r="D46">
-        <v>12.37040001822674</v>
+        <v>12.19912343176492</v>
       </c>
       <c r="E46">
-        <v>13.71304</v>
+        <v>14.03245</v>
       </c>
       <c r="F46">
-        <v>14.05404</v>
+        <v>14.37345</v>
       </c>
       <c r="G46">
         <v>0.008</v>
@@ -5155,37 +5155,37 @@
         <v>0.099</v>
       </c>
       <c r="M46">
-        <v>3.313942632</v>
+        <v>3.38925951</v>
       </c>
       <c r="N46">
-        <v>-3.214942632</v>
+        <v>-3.29025951</v>
       </c>
       <c r="O46">
-        <v>-0.61083910008</v>
+        <v>-0.6251493069</v>
       </c>
       <c r="P46">
-        <v>-2.60410353192</v>
+        <v>-2.6651102031</v>
       </c>
       <c r="Q46">
-        <v>-2.70310353192</v>
+        <v>-2.7641102031</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1392211208213673</v>
+        <v>0.1409196866544831</v>
       </c>
       <c r="T46">
-        <v>1.711040635985833</v>
+        <v>1.74215046573103</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.005676018594397925</v>
+        <v>0.005549884847855749</v>
       </c>
       <c r="W46">
-        <v>0.234461594815441</v>
+        <v>0.2344913371528756</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.02987378207577862</v>
+        <v>0.02920992025187241</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1830269293787598</v>
+        <v>0.1849269293787598</v>
       </c>
       <c r="C47">
-        <v>-2.166326568235085</v>
+        <v>-2.652335045063772</v>
       </c>
       <c r="D47">
-        <v>12.19912343176492</v>
+        <v>12.03252495493623</v>
       </c>
       <c r="E47">
-        <v>14.03245</v>
+        <v>14.35186</v>
       </c>
       <c r="F47">
-        <v>14.37345</v>
+        <v>14.69286</v>
       </c>
       <c r="G47">
         <v>0.008</v>
@@ -5237,37 +5237,37 @@
         <v>0.099</v>
       </c>
       <c r="M47">
-        <v>3.38925951</v>
+        <v>3.464576388000001</v>
       </c>
       <c r="N47">
-        <v>-3.29025951</v>
+        <v>-3.365576388</v>
       </c>
       <c r="O47">
-        <v>-0.6251493069</v>
+        <v>-0.6394595137200001</v>
       </c>
       <c r="P47">
-        <v>-2.6651102031</v>
+        <v>-2.726116874280001</v>
       </c>
       <c r="Q47">
-        <v>-2.7641102031</v>
+        <v>-2.825116874280001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1409196866544831</v>
+        <v>0.1426811623332698</v>
       </c>
       <c r="T47">
-        <v>1.74215046573103</v>
+        <v>1.774412511392715</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.005549884847855749</v>
+        <v>0.005429235177250188</v>
       </c>
       <c r="W47">
-        <v>0.2344913371528756</v>
+        <v>0.2345197863452044</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.02920992025187241</v>
+        <v>0.02857492198552736</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5283,22 +5283,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1849269293787598</v>
+        <v>0.1868269293787597</v>
       </c>
       <c r="C48">
-        <v>-2.652335045063772</v>
+        <v>-3.133854491217694</v>
       </c>
       <c r="D48">
-        <v>12.03252495493623</v>
+        <v>11.87041550878231</v>
       </c>
       <c r="E48">
-        <v>14.35186</v>
+        <v>14.67127</v>
       </c>
       <c r="F48">
-        <v>14.69286</v>
+        <v>15.01227</v>
       </c>
       <c r="G48">
         <v>0.008</v>
@@ -5319,37 +5319,37 @@
         <v>0.099</v>
       </c>
       <c r="M48">
-        <v>3.464576388000001</v>
+        <v>3.539893266000001</v>
       </c>
       <c r="N48">
-        <v>-3.365576388</v>
+        <v>-3.440893266000001</v>
       </c>
       <c r="O48">
-        <v>-0.6394595137200001</v>
+        <v>-0.6537697205400002</v>
       </c>
       <c r="P48">
-        <v>-2.726116874280001</v>
+        <v>-2.787123545460001</v>
       </c>
       <c r="Q48">
-        <v>-2.825116874280001</v>
+        <v>-2.886123545460001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1426811623332698</v>
+        <v>0.1445091087923881</v>
       </c>
       <c r="T48">
-        <v>1.774412511392715</v>
+        <v>1.807891992739748</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.005429235177250188</v>
+        <v>0.005313719535181036</v>
       </c>
       <c r="W48">
-        <v>0.2345197863452044</v>
+        <v>0.2345470249336043</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.02857492198552736</v>
+        <v>0.02796694492200547</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5365,22 +5365,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1868269293787597</v>
+        <v>0.1887269293787597</v>
       </c>
       <c r="C49">
-        <v>-3.133854491217694</v>
+        <v>-3.611063931566111</v>
       </c>
       <c r="D49">
-        <v>11.87041550878231</v>
+        <v>11.71261606843389</v>
       </c>
       <c r="E49">
-        <v>14.67127</v>
+        <v>14.99068</v>
       </c>
       <c r="F49">
-        <v>15.01227</v>
+        <v>15.33168</v>
       </c>
       <c r="G49">
         <v>0.008</v>
@@ -5401,37 +5401,37 @@
         <v>0.099</v>
       </c>
       <c r="M49">
-        <v>3.539893266000001</v>
+        <v>3.615210144000001</v>
       </c>
       <c r="N49">
-        <v>-3.440893266000001</v>
+        <v>-3.516210144</v>
       </c>
       <c r="O49">
-        <v>-0.6537697205400002</v>
+        <v>-0.6680799273600001</v>
       </c>
       <c r="P49">
-        <v>-2.787123545460001</v>
+        <v>-2.84813021664</v>
       </c>
       <c r="Q49">
-        <v>-2.886123545460001</v>
+        <v>-2.947130216640001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1445091087923881</v>
+        <v>0.1464073608845494</v>
       </c>
       <c r="T49">
-        <v>1.807891992739748</v>
+        <v>1.842659146446281</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.005313719535181036</v>
+        <v>0.005203017044864765</v>
       </c>
       <c r="W49">
-        <v>0.2345470249336043</v>
+        <v>0.2345731285808209</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.02796694492200547</v>
+        <v>0.02738430023613037</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5447,22 +5447,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1887269293787597</v>
+        <v>0.1906269293787597</v>
       </c>
       <c r="C50">
-        <v>-3.611063931566109</v>
+        <v>-4.084132996392546</v>
       </c>
       <c r="D50">
-        <v>11.71261606843389</v>
+        <v>11.55895700360746</v>
       </c>
       <c r="E50">
-        <v>14.99068</v>
+        <v>15.31009</v>
       </c>
       <c r="F50">
-        <v>15.33168</v>
+        <v>15.65109</v>
       </c>
       <c r="G50">
         <v>0.008</v>
@@ -5483,37 +5483,37 @@
         <v>0.099</v>
       </c>
       <c r="M50">
-        <v>3.615210144</v>
+        <v>3.690527022</v>
       </c>
       <c r="N50">
-        <v>-3.516210144</v>
+        <v>-3.591527022</v>
       </c>
       <c r="O50">
-        <v>-0.66807992736</v>
+        <v>-0.6823901341800001</v>
       </c>
       <c r="P50">
-        <v>-2.84813021664</v>
+        <v>-2.90913688782</v>
       </c>
       <c r="Q50">
-        <v>-2.94713021664</v>
+        <v>-3.00813688782</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1464073608845494</v>
+        <v>0.1483800542352269</v>
       </c>
       <c r="T50">
-        <v>1.842659146446281</v>
+        <v>1.878789717945228</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.005203017044864765</v>
+        <v>0.005096833023540993</v>
       </c>
       <c r="W50">
-        <v>0.2345731285808209</v>
+        <v>0.234598166773049</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.02738430023613037</v>
+        <v>0.02682543696600526</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5529,22 +5529,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1906269293787597</v>
+        <v>0.1925269293787598</v>
       </c>
       <c r="C51">
-        <v>-4.084132996392546</v>
+        <v>-4.553222529657784</v>
       </c>
       <c r="D51">
-        <v>11.55895700360746</v>
+        <v>11.40927747034222</v>
       </c>
       <c r="E51">
-        <v>15.31009</v>
+        <v>15.6295</v>
       </c>
       <c r="F51">
-        <v>15.65109</v>
+        <v>15.9705</v>
       </c>
       <c r="G51">
         <v>0.008</v>
@@ -5565,37 +5565,37 @@
         <v>0.099</v>
       </c>
       <c r="M51">
-        <v>3.690527022</v>
+        <v>3.765843900000001</v>
       </c>
       <c r="N51">
-        <v>-3.591527022</v>
+        <v>-3.6668439</v>
       </c>
       <c r="O51">
-        <v>-0.6823901341800001</v>
+        <v>-0.6967003410000001</v>
       </c>
       <c r="P51">
-        <v>-2.90913688782</v>
+        <v>-2.970143559</v>
       </c>
       <c r="Q51">
-        <v>-3.00813688782</v>
+        <v>-3.069143559</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1483800542352269</v>
+        <v>0.1504316553199314</v>
       </c>
       <c r="T51">
-        <v>1.878789717945228</v>
+        <v>1.916365512304133</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.005096833023540993</v>
+        <v>0.004994896363070174</v>
       </c>
       <c r="W51">
-        <v>0.234598166773049</v>
+        <v>0.2346222034375881</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.02682543696600526</v>
+        <v>0.02628892822668516</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5611,22 +5611,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1925269293787598</v>
+        <v>0.1944269293787597</v>
       </c>
       <c r="C52">
-        <v>-4.553222529657784</v>
+        <v>-5.018485150607837</v>
       </c>
       <c r="D52">
-        <v>11.40927747034222</v>
+        <v>11.26342484939217</v>
       </c>
       <c r="E52">
-        <v>15.6295</v>
+        <v>15.94891</v>
       </c>
       <c r="F52">
-        <v>15.9705</v>
+        <v>16.28991</v>
       </c>
       <c r="G52">
         <v>0.008</v>
@@ -5647,37 +5647,37 @@
         <v>0.099</v>
       </c>
       <c r="M52">
-        <v>3.765843900000001</v>
+        <v>3.841160778000001</v>
       </c>
       <c r="N52">
-        <v>-3.6668439</v>
+        <v>-3.742160778000001</v>
       </c>
       <c r="O52">
-        <v>-0.6967003410000001</v>
+        <v>-0.7110105478200002</v>
       </c>
       <c r="P52">
-        <v>-2.970143559</v>
+        <v>-3.031150230180001</v>
       </c>
       <c r="Q52">
-        <v>-3.069143559</v>
+        <v>-3.130150230180001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1504316553199314</v>
+        <v>0.1525669952244198</v>
       </c>
       <c r="T52">
-        <v>1.916365512304133</v>
+        <v>1.955475012555237</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.004994896363070174</v>
+        <v>0.004896957218696248</v>
       </c>
       <c r="W52">
-        <v>0.2346222034375881</v>
+        <v>0.2346452974878314</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.02628892822668516</v>
+        <v>0.02577345904576978</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5693,22 +5693,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1944269293787597</v>
+        <v>0.1963269293787597</v>
       </c>
       <c r="C53">
-        <v>-5.018485150607837</v>
+        <v>-5.480065772849096</v>
       </c>
       <c r="D53">
-        <v>11.26342484939217</v>
+        <v>11.1212542271509</v>
       </c>
       <c r="E53">
-        <v>15.94891</v>
+        <v>16.26832</v>
       </c>
       <c r="F53">
-        <v>16.28991</v>
+        <v>16.60932</v>
       </c>
       <c r="G53">
         <v>0.008</v>
@@ -5729,37 +5729,37 @@
         <v>0.099</v>
       </c>
       <c r="M53">
-        <v>3.841160778000001</v>
+        <v>3.916477656</v>
       </c>
       <c r="N53">
-        <v>-3.742160778000001</v>
+        <v>-3.817477656</v>
       </c>
       <c r="O53">
-        <v>-0.7110105478200002</v>
+        <v>-0.72532075464</v>
       </c>
       <c r="P53">
-        <v>-3.031150230180001</v>
+        <v>-3.09215690136</v>
       </c>
       <c r="Q53">
-        <v>-3.130150230180001</v>
+        <v>-3.19115690136</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1525669952244198</v>
+        <v>0.1547913076249286</v>
       </c>
       <c r="T53">
-        <v>1.955475012555237</v>
+        <v>1.996214075316805</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.004896957218696248</v>
+        <v>0.004802784964490553</v>
       </c>
       <c r="W53">
-        <v>0.2346452974878314</v>
+        <v>0.2346675033053731</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.02577345904576978</v>
+        <v>0.02527781560258191</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5775,22 +5775,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1963269293787597</v>
+        <v>0.1982269293787597</v>
       </c>
       <c r="C54">
-        <v>-5.480065772849096</v>
+        <v>-5.93810208460193</v>
       </c>
       <c r="D54">
-        <v>11.1212542271509</v>
+        <v>10.98262791539807</v>
       </c>
       <c r="E54">
-        <v>16.26832</v>
+        <v>16.58773</v>
       </c>
       <c r="F54">
-        <v>16.60932</v>
+        <v>16.92873</v>
       </c>
       <c r="G54">
         <v>0.008</v>
@@ -5811,37 +5811,37 @@
         <v>0.099</v>
       </c>
       <c r="M54">
-        <v>3.916477656</v>
+        <v>3.991794534000001</v>
       </c>
       <c r="N54">
-        <v>-3.817477656</v>
+        <v>-3.892794534000001</v>
       </c>
       <c r="O54">
-        <v>-0.72532075464</v>
+        <v>-0.7396309614600001</v>
       </c>
       <c r="P54">
-        <v>-3.09215690136</v>
+        <v>-3.15316357254</v>
       </c>
       <c r="Q54">
-        <v>-3.19115690136</v>
+        <v>-3.252163572540001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1547913076249286</v>
+        <v>0.1571102716169483</v>
       </c>
       <c r="T54">
-        <v>1.996214075316805</v>
+        <v>2.038686715217163</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.004802784964490553</v>
+        <v>0.004712166380254881</v>
       </c>
       <c r="W54">
-        <v>0.2346675033053731</v>
+        <v>0.2346888711675359</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.02527781560258191</v>
+        <v>0.024800875685552</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5857,22 +5857,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1982269293787597</v>
+        <v>0.2001269293787597</v>
       </c>
       <c r="C55">
-        <v>-5.93810208460193</v>
+        <v>-6.392724993478272</v>
       </c>
       <c r="D55">
-        <v>10.98262791539807</v>
+        <v>10.84741500652173</v>
       </c>
       <c r="E55">
-        <v>16.58773</v>
+        <v>16.90714</v>
       </c>
       <c r="F55">
-        <v>16.92873</v>
+        <v>17.24814</v>
       </c>
       <c r="G55">
         <v>0.008</v>
@@ -5893,37 +5893,37 @@
         <v>0.099</v>
       </c>
       <c r="M55">
-        <v>3.991794534000001</v>
+        <v>4.067111412000001</v>
       </c>
       <c r="N55">
-        <v>-3.892794534000001</v>
+        <v>-3.968111412000001</v>
       </c>
       <c r="O55">
-        <v>-0.7396309614600001</v>
+        <v>-0.7539411682800001</v>
       </c>
       <c r="P55">
-        <v>-3.15316357254</v>
+        <v>-3.214170243720001</v>
       </c>
       <c r="Q55">
-        <v>-3.252163572540001</v>
+        <v>-3.313170243720001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1571102716169483</v>
+        <v>0.1595300601303602</v>
       </c>
       <c r="T55">
-        <v>2.038686715217163</v>
+        <v>2.083005991634927</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.004712166380254881</v>
+        <v>0.00462490403987979</v>
       </c>
       <c r="W55">
-        <v>0.2346888711675359</v>
+        <v>0.2347094476273963</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.024800875685552</v>
+        <v>0.02434160020989373</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2001269293787597</v>
+        <v>0.2020269293787598</v>
       </c>
       <c r="C56">
-        <v>-6.392724993478272</v>
+        <v>-6.844059038803548</v>
       </c>
       <c r="D56">
-        <v>10.84741500652173</v>
+        <v>10.71549096119646</v>
       </c>
       <c r="E56">
-        <v>16.90714</v>
+        <v>17.22655</v>
       </c>
       <c r="F56">
-        <v>17.24814</v>
+        <v>17.56755</v>
       </c>
       <c r="G56">
         <v>0.008</v>
@@ -5975,37 +5975,37 @@
         <v>0.099</v>
       </c>
       <c r="M56">
-        <v>4.067111412000001</v>
+        <v>4.142428290000002</v>
       </c>
       <c r="N56">
-        <v>-3.968111412000001</v>
+        <v>-4.043428290000001</v>
       </c>
       <c r="O56">
-        <v>-0.7539411682800001</v>
+        <v>-0.7682513751000003</v>
       </c>
       <c r="P56">
-        <v>-3.214170243720001</v>
+        <v>-3.275176914900001</v>
       </c>
       <c r="Q56">
-        <v>-3.313170243720001</v>
+        <v>-3.374176914900001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1595300601303602</v>
+        <v>0.1620573947999238</v>
       </c>
       <c r="T56">
-        <v>2.083005991634927</v>
+        <v>2.129295013671259</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.00462490403987979</v>
+        <v>0.004540814875518339</v>
       </c>
       <c r="W56">
-        <v>0.2347094476273963</v>
+        <v>0.2347292758523528</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.02434160020989373</v>
+        <v>0.02389902566062285</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6021,22 +6021,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2020269293787598</v>
+        <v>0.2039269293787598</v>
       </c>
       <c r="C57">
-        <v>-6.844059038803548</v>
+        <v>-7.292222774212561</v>
       </c>
       <c r="D57">
-        <v>10.71549096119646</v>
+        <v>10.58673722578744</v>
       </c>
       <c r="E57">
-        <v>17.22655</v>
+        <v>17.54596</v>
       </c>
       <c r="F57">
-        <v>17.56755</v>
+        <v>17.88696</v>
       </c>
       <c r="G57">
         <v>0.008</v>
@@ -6057,37 +6057,37 @@
         <v>0.099</v>
       </c>
       <c r="M57">
-        <v>4.142428290000002</v>
+        <v>4.217745168</v>
       </c>
       <c r="N57">
-        <v>-4.043428290000001</v>
+        <v>-4.118745168</v>
       </c>
       <c r="O57">
-        <v>-0.7682513751000003</v>
+        <v>-0.78256158192</v>
       </c>
       <c r="P57">
-        <v>-3.275176914900001</v>
+        <v>-3.33618358608</v>
       </c>
       <c r="Q57">
-        <v>-3.374176914900001</v>
+        <v>-3.43518358608</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1620573947999238</v>
+        <v>0.1646996083181039</v>
       </c>
       <c r="T57">
-        <v>2.129295013671259</v>
+        <v>2.177688082163787</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.004540814875518339</v>
+        <v>0.004459728895598369</v>
       </c>
       <c r="W57">
-        <v>0.2347292758523528</v>
+        <v>0.2347483959264179</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.02389902566062285</v>
+        <v>0.0234722573452546</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6103,22 +6103,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2039269293787598</v>
+        <v>0.2058269293787597</v>
       </c>
       <c r="C58">
-        <v>-7.292222774212561</v>
+        <v>-7.737329122990133</v>
       </c>
       <c r="D58">
-        <v>10.58673722578744</v>
+        <v>10.46104087700987</v>
       </c>
       <c r="E58">
-        <v>17.54596</v>
+        <v>17.86537</v>
       </c>
       <c r="F58">
-        <v>17.88696</v>
+        <v>18.20637</v>
       </c>
       <c r="G58">
         <v>0.008</v>
@@ -6139,37 +6139,37 @@
         <v>0.099</v>
       </c>
       <c r="M58">
-        <v>4.217745168</v>
+        <v>4.293062046000001</v>
       </c>
       <c r="N58">
-        <v>-4.118745168</v>
+        <v>-4.194062046000001</v>
       </c>
       <c r="O58">
-        <v>-0.78256158192</v>
+        <v>-0.7968717887400002</v>
       </c>
       <c r="P58">
-        <v>-3.33618358608</v>
+        <v>-3.397190257260001</v>
       </c>
       <c r="Q58">
-        <v>-3.43518358608</v>
+        <v>-3.496190257260001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1646996083181039</v>
+        <v>0.1674647154882924</v>
       </c>
       <c r="T58">
-        <v>2.177688082163787</v>
+        <v>2.228331991051317</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.004459728895598369</v>
+        <v>0.004381488037780853</v>
       </c>
       <c r="W58">
-        <v>0.2347483959264179</v>
+        <v>0.2347668451206913</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.0234722573452546</v>
+        <v>0.02306046335674139</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6185,22 +6185,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2058269293787597</v>
+        <v>0.2077269293787598</v>
       </c>
       <c r="C59">
-        <v>-7.737329122990133</v>
+        <v>-8.179485708394886</v>
       </c>
       <c r="D59">
-        <v>10.46104087700987</v>
+        <v>10.33829429160512</v>
       </c>
       <c r="E59">
-        <v>17.86537</v>
+        <v>18.18478</v>
       </c>
       <c r="F59">
-        <v>18.20637</v>
+        <v>18.52578</v>
       </c>
       <c r="G59">
         <v>0.008</v>
@@ -6221,37 +6221,37 @@
         <v>0.099</v>
       </c>
       <c r="M59">
-        <v>4.293062046000001</v>
+        <v>4.368378924000001</v>
       </c>
       <c r="N59">
-        <v>-4.194062046000001</v>
+        <v>-4.269378924000001</v>
       </c>
       <c r="O59">
-        <v>-0.7968717887400002</v>
+        <v>-0.8111819955600001</v>
       </c>
       <c r="P59">
-        <v>-3.397190257260001</v>
+        <v>-3.45819692844</v>
       </c>
       <c r="Q59">
-        <v>-3.496190257260001</v>
+        <v>-3.557196928440001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1674647154882924</v>
+        <v>0.1703614944284898</v>
       </c>
       <c r="T59">
-        <v>2.228331991051317</v>
+        <v>2.281387514647777</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.004381488037780853</v>
+        <v>0.004305945140577735</v>
       </c>
       <c r="W59">
-        <v>0.2347668451206913</v>
+        <v>0.2347846581358518</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.02306046335674139</v>
+        <v>0.02266286916093552</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2077269293787597</v>
+        <v>0.2096269293787597</v>
       </c>
       <c r="C60">
-        <v>-8.179485708394882</v>
+        <v>-8.618795160997303</v>
       </c>
       <c r="D60">
-        <v>10.33829429160512</v>
+        <v>10.2183948390027</v>
       </c>
       <c r="E60">
-        <v>18.18478</v>
+        <v>18.50419</v>
       </c>
       <c r="F60">
-        <v>18.52578</v>
+        <v>18.84519</v>
       </c>
       <c r="G60">
         <v>0.008</v>
@@ -6303,37 +6303,37 @@
         <v>0.099</v>
       </c>
       <c r="M60">
-        <v>4.368378924000001</v>
+        <v>4.443695802</v>
       </c>
       <c r="N60">
-        <v>-4.269378924000001</v>
+        <v>-4.344695801999999</v>
       </c>
       <c r="O60">
-        <v>-0.8111819955600001</v>
+        <v>-0.8254922023799999</v>
       </c>
       <c r="P60">
-        <v>-3.45819692844</v>
+        <v>-3.51920359962</v>
       </c>
       <c r="Q60">
-        <v>-3.557196928440001</v>
+        <v>-3.61820359962</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1703614944284898</v>
+        <v>0.173399579658453</v>
       </c>
       <c r="T60">
-        <v>2.281387514647776</v>
+        <v>2.337031112566015</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.004305945140577735</v>
+        <v>0.004232963019550996</v>
       </c>
       <c r="W60">
-        <v>0.2347846581358518</v>
+        <v>0.2348018673199899</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.02266286916093552</v>
+        <v>0.02227875273447899</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6349,22 +6349,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2096269293787597</v>
+        <v>0.2115269293787597</v>
       </c>
       <c r="C61">
-        <v>-8.618795160997303</v>
+        <v>-9.055355404876702</v>
       </c>
       <c r="D61">
-        <v>10.2183948390027</v>
+        <v>10.1012445951233</v>
       </c>
       <c r="E61">
-        <v>18.50419</v>
+        <v>18.8236</v>
       </c>
       <c r="F61">
-        <v>18.84519</v>
+        <v>19.1646</v>
       </c>
       <c r="G61">
         <v>0.008</v>
@@ -6385,37 +6385,37 @@
         <v>0.099</v>
       </c>
       <c r="M61">
-        <v>4.443695802</v>
+        <v>4.51901268</v>
       </c>
       <c r="N61">
-        <v>-4.344695801999999</v>
+        <v>-4.42001268</v>
       </c>
       <c r="O61">
-        <v>-0.8254922023799999</v>
+        <v>-0.8398024092</v>
       </c>
       <c r="P61">
-        <v>-3.51920359962</v>
+        <v>-3.5802102708</v>
       </c>
       <c r="Q61">
-        <v>-3.61820359962</v>
+        <v>-3.679210270800001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.173399579658453</v>
+        <v>0.1765895691499142</v>
       </c>
       <c r="T61">
-        <v>2.337031112566015</v>
+        <v>2.395456890380165</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.004232963019550996</v>
+        <v>0.004162413635891812</v>
       </c>
       <c r="W61">
-        <v>0.2348018673199899</v>
+        <v>0.2348185028646567</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.02227875273447899</v>
+        <v>0.02190744018890434</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6431,22 +6431,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2115269293787597</v>
+        <v>0.2134269293787597</v>
       </c>
       <c r="C62">
-        <v>-9.055355404876702</v>
+        <v>-9.489259924354348</v>
       </c>
       <c r="D62">
-        <v>10.1012445951233</v>
+        <v>9.986750075645654</v>
       </c>
       <c r="E62">
-        <v>18.8236</v>
+        <v>19.14301</v>
       </c>
       <c r="F62">
-        <v>19.1646</v>
+        <v>19.48401</v>
       </c>
       <c r="G62">
         <v>0.008</v>
@@ -6467,37 +6467,37 @@
         <v>0.099</v>
       </c>
       <c r="M62">
-        <v>4.51901268</v>
+        <v>4.594329558</v>
       </c>
       <c r="N62">
-        <v>-4.42001268</v>
+        <v>-4.495329558</v>
       </c>
       <c r="O62">
-        <v>-0.8398024092</v>
+        <v>-0.85411261602</v>
       </c>
       <c r="P62">
-        <v>-3.5802102708</v>
+        <v>-3.64121694198</v>
       </c>
       <c r="Q62">
-        <v>-3.679210270800001</v>
+        <v>-3.74021694198</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1765895691499142</v>
+        <v>0.1799431478460659</v>
       </c>
       <c r="T62">
-        <v>2.395456890380165</v>
+        <v>2.456878861928375</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.004162413635891812</v>
+        <v>0.004094177346778831</v>
       </c>
       <c r="W62">
-        <v>0.2348185028646567</v>
+        <v>0.2348345929816296</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.02190744018890434</v>
+        <v>0.02154830182515177</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6513,22 +6513,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2134269293787597</v>
+        <v>0.2153269293787597</v>
       </c>
       <c r="C63">
-        <v>-9.489259924354348</v>
+        <v>-9.920598012789982</v>
       </c>
       <c r="D63">
-        <v>9.986750075645654</v>
+        <v>9.874821987210021</v>
       </c>
       <c r="E63">
-        <v>19.14301</v>
+        <v>19.46242</v>
       </c>
       <c r="F63">
-        <v>19.48401</v>
+        <v>19.80342</v>
       </c>
       <c r="G63">
         <v>0.008</v>
@@ -6549,37 +6549,37 @@
         <v>0.099</v>
       </c>
       <c r="M63">
-        <v>4.594329558</v>
+        <v>4.669646436000001</v>
       </c>
       <c r="N63">
-        <v>-4.495329558</v>
+        <v>-4.570646436000001</v>
       </c>
       <c r="O63">
-        <v>-0.85411261602</v>
+        <v>-0.8684228228400002</v>
       </c>
       <c r="P63">
-        <v>-3.64121694198</v>
+        <v>-3.70222361316</v>
       </c>
       <c r="Q63">
-        <v>-3.74021694198</v>
+        <v>-3.80122361316</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1799431478460659</v>
+        <v>0.1834732306841203</v>
       </c>
       <c r="T63">
-        <v>2.456878861928375</v>
+        <v>2.521533568821227</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.004094177346778831</v>
+        <v>0.004028142228282398</v>
       </c>
       <c r="W63">
-        <v>0.2348345929816296</v>
+        <v>0.234850164062571</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.02154830182515177</v>
+        <v>0.02120074856990739</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6595,22 +6595,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2153269293787597</v>
+        <v>0.2172269293787598</v>
       </c>
       <c r="C64">
-        <v>-9.920598012789982</v>
+        <v>-10.34945500483313</v>
       </c>
       <c r="D64">
-        <v>9.874821987210021</v>
+        <v>9.765374995166869</v>
       </c>
       <c r="E64">
-        <v>19.46242</v>
+        <v>19.78183</v>
       </c>
       <c r="F64">
-        <v>19.80342</v>
+        <v>20.12283</v>
       </c>
       <c r="G64">
         <v>0.008</v>
@@ -6631,37 +6631,37 @@
         <v>0.099</v>
       </c>
       <c r="M64">
-        <v>4.669646436000001</v>
+        <v>4.744963314</v>
       </c>
       <c r="N64">
-        <v>-4.570646436000001</v>
+        <v>-4.645963314</v>
       </c>
       <c r="O64">
-        <v>-0.8684228228400002</v>
+        <v>-0.8827330296600001</v>
       </c>
       <c r="P64">
-        <v>-3.70222361316</v>
+        <v>-3.76323028434</v>
       </c>
       <c r="Q64">
-        <v>-3.80122361316</v>
+        <v>-3.86223028434</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1834732306841203</v>
+        <v>0.1871941288107181</v>
       </c>
       <c r="T64">
-        <v>2.521533568821227</v>
+        <v>2.589683124735314</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.004028142228282398</v>
+        <v>0.003964203462754106</v>
       </c>
       <c r="W64">
-        <v>0.234850164062571</v>
+        <v>0.2348652408234826</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.02120074856990739</v>
+        <v>0.02086422875133742</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6677,22 +6677,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2172269293787598</v>
+        <v>0.2191269293787597</v>
       </c>
       <c r="C65">
-        <v>-10.34945500483313</v>
+        <v>-10.77591249339893</v>
       </c>
       <c r="D65">
-        <v>9.765374995166869</v>
+        <v>9.658327506601076</v>
       </c>
       <c r="E65">
-        <v>19.78183</v>
+        <v>20.10124</v>
       </c>
       <c r="F65">
-        <v>20.12283</v>
+        <v>20.44224</v>
       </c>
       <c r="G65">
         <v>0.008</v>
@@ -6713,37 +6713,37 @@
         <v>0.099</v>
       </c>
       <c r="M65">
-        <v>4.744963314</v>
+        <v>4.820280192</v>
       </c>
       <c r="N65">
-        <v>-4.645963314</v>
+        <v>-4.721280192</v>
       </c>
       <c r="O65">
-        <v>-0.8827330296600001</v>
+        <v>-0.8970432364800001</v>
       </c>
       <c r="P65">
-        <v>-3.76323028434</v>
+        <v>-3.82423695552</v>
       </c>
       <c r="Q65">
-        <v>-3.86223028434</v>
+        <v>-3.92323695552</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1871941288107181</v>
+        <v>0.1911217434999047</v>
       </c>
       <c r="T65">
-        <v>2.589683124735314</v>
+        <v>2.661618767089073</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.003964203462754106</v>
+        <v>0.003902262783648573</v>
       </c>
       <c r="W65">
-        <v>0.2348652408234826</v>
+        <v>0.2348798464356157</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.02086422875133742</v>
+        <v>0.0205382251770978</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6759,22 +6759,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2191269293787597</v>
+        <v>0.2210269293787597</v>
       </c>
       <c r="C66">
-        <v>-10.77591249339893</v>
+        <v>-11.20004853252774</v>
       </c>
       <c r="D66">
-        <v>9.658327506601076</v>
+        <v>9.553601467472262</v>
       </c>
       <c r="E66">
-        <v>20.10124</v>
+        <v>20.42065</v>
       </c>
       <c r="F66">
-        <v>20.44224</v>
+        <v>20.76165</v>
       </c>
       <c r="G66">
         <v>0.008</v>
@@ -6795,37 +6795,37 @@
         <v>0.099</v>
       </c>
       <c r="M66">
-        <v>4.820280192</v>
+        <v>4.895597070000001</v>
       </c>
       <c r="N66">
-        <v>-4.721280192</v>
+        <v>-4.796597070000001</v>
       </c>
       <c r="O66">
-        <v>-0.8970432364800001</v>
+        <v>-0.9113534433000001</v>
       </c>
       <c r="P66">
-        <v>-3.82423695552</v>
+        <v>-3.8852436267</v>
       </c>
       <c r="Q66">
-        <v>-3.92323695552</v>
+        <v>-3.984243626700001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1911217434999047</v>
+        <v>0.1952737933141878</v>
       </c>
       <c r="T66">
-        <v>2.661618767089073</v>
+        <v>2.737665017577333</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.003902262783648573</v>
+        <v>0.003842227971592441</v>
       </c>
       <c r="W66">
-        <v>0.2348798464356157</v>
+        <v>0.2348940026442985</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.0205382251770978</v>
+        <v>0.02022225248206555</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6841,22 +6841,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2210269293787597</v>
+        <v>0.2229269293787597</v>
       </c>
       <c r="C67">
-        <v>-11.20004853252774</v>
+        <v>-11.6219378271887</v>
       </c>
       <c r="D67">
-        <v>9.553601467472262</v>
+        <v>9.451122172811301</v>
       </c>
       <c r="E67">
-        <v>20.42065</v>
+        <v>20.74006</v>
       </c>
       <c r="F67">
-        <v>20.76165</v>
+        <v>21.08106</v>
       </c>
       <c r="G67">
         <v>0.008</v>
@@ -6877,37 +6877,37 @@
         <v>0.099</v>
       </c>
       <c r="M67">
-        <v>4.895597070000001</v>
+        <v>4.970913948000002</v>
       </c>
       <c r="N67">
-        <v>-4.796597070000001</v>
+        <v>-4.871913948000001</v>
       </c>
       <c r="O67">
-        <v>-0.9113534433000001</v>
+        <v>-0.9256636501200003</v>
       </c>
       <c r="P67">
-        <v>-3.8852436267</v>
+        <v>-3.946250297880001</v>
       </c>
       <c r="Q67">
-        <v>-3.984243626700001</v>
+        <v>-4.045250297880001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1952737933141878</v>
+        <v>0.1996700813528403</v>
       </c>
       <c r="T67">
-        <v>2.737665017577333</v>
+        <v>2.818184576917842</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.003842227971592441</v>
+        <v>0.003784012396265283</v>
       </c>
       <c r="W67">
-        <v>0.2348940026442985</v>
+        <v>0.2349077298769607</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.02022225248206555</v>
+        <v>0.01991585471718571</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6923,22 +6923,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2229269293787597</v>
+        <v>0.2248269293787598</v>
       </c>
       <c r="C68">
-        <v>-11.6219378271887</v>
+        <v>-12.04165191099696</v>
       </c>
       <c r="D68">
-        <v>9.451122172811301</v>
+        <v>9.350818089003043</v>
       </c>
       <c r="E68">
-        <v>20.74006</v>
+        <v>21.05947</v>
       </c>
       <c r="F68">
-        <v>21.08106</v>
+        <v>21.40047</v>
       </c>
       <c r="G68">
         <v>0.008</v>
@@ -6959,37 +6959,37 @@
         <v>0.099</v>
       </c>
       <c r="M68">
-        <v>4.970913948000002</v>
+        <v>5.046230826</v>
       </c>
       <c r="N68">
-        <v>-4.871913948000001</v>
+        <v>-4.947230826</v>
       </c>
       <c r="O68">
-        <v>-0.9256636501200003</v>
+        <v>-0.93997385694</v>
       </c>
       <c r="P68">
-        <v>-3.946250297880001</v>
+        <v>-4.00725696906</v>
       </c>
       <c r="Q68">
-        <v>-4.045250297880001</v>
+        <v>-4.10625696906</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1996700813528403</v>
+        <v>0.2043328110908052</v>
       </c>
       <c r="T68">
-        <v>2.818184576917842</v>
+        <v>2.903584109551716</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.003784012396265283</v>
+        <v>0.0037275345993061</v>
       </c>
       <c r="W68">
-        <v>0.2349077298769607</v>
+        <v>0.2349210473414836</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.01991585471718571</v>
+        <v>0.01961860315424269</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7005,22 +7005,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2248269293787598</v>
+        <v>0.2267269293787597</v>
       </c>
       <c r="C69">
-        <v>-12.04165191099696</v>
+        <v>-12.45925931273317</v>
       </c>
       <c r="D69">
-        <v>9.350818089003043</v>
+        <v>9.252620687266832</v>
       </c>
       <c r="E69">
-        <v>21.05947</v>
+        <v>21.37888</v>
       </c>
       <c r="F69">
-        <v>21.40047</v>
+        <v>21.71988</v>
       </c>
       <c r="G69">
         <v>0.008</v>
@@ -7041,37 +7041,37 @@
         <v>0.099</v>
       </c>
       <c r="M69">
-        <v>5.046230826</v>
+        <v>5.121547704000001</v>
       </c>
       <c r="N69">
-        <v>-4.947230826</v>
+        <v>-5.022547704000001</v>
       </c>
       <c r="O69">
-        <v>-0.93997385694</v>
+        <v>-0.9542840637600002</v>
       </c>
       <c r="P69">
-        <v>-4.00725696906</v>
+        <v>-4.068263640240001</v>
       </c>
       <c r="Q69">
-        <v>-4.10625696906</v>
+        <v>-4.167263640240001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2043328110908052</v>
+        <v>0.2092869614373928</v>
       </c>
       <c r="T69">
-        <v>2.903584109551716</v>
+        <v>2.994321112975207</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0037275345993061</v>
+        <v>0.003672717914022186</v>
       </c>
       <c r="W69">
-        <v>0.2349210473414836</v>
+        <v>0.2349339731158736</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.01961860315424269</v>
+        <v>0.0193300942843273</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7087,22 +7087,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2267269293787597</v>
+        <v>0.2286269293787598</v>
       </c>
       <c r="C70">
-        <v>-12.45925931273317</v>
+        <v>-12.87482571247988</v>
       </c>
       <c r="D70">
-        <v>9.252620687266832</v>
+        <v>9.156464287520121</v>
       </c>
       <c r="E70">
-        <v>21.37888</v>
+        <v>21.69829</v>
       </c>
       <c r="F70">
-        <v>21.71988</v>
+        <v>22.03929</v>
       </c>
       <c r="G70">
         <v>0.008</v>
@@ -7123,37 +7123,37 @@
         <v>0.099</v>
       </c>
       <c r="M70">
-        <v>5.121547704000001</v>
+        <v>5.196864582000002</v>
       </c>
       <c r="N70">
-        <v>-5.022547704000001</v>
+        <v>-5.097864582000001</v>
       </c>
       <c r="O70">
-        <v>-0.9542840637600002</v>
+        <v>-0.9685942705800002</v>
       </c>
       <c r="P70">
-        <v>-4.068263640240001</v>
+        <v>-4.129270311420001</v>
       </c>
       <c r="Q70">
-        <v>-4.167263640240001</v>
+        <v>-4.228270311420001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2092869614373928</v>
+        <v>0.2145607343869862</v>
       </c>
       <c r="T70">
-        <v>2.994321112975207</v>
+        <v>3.090912116619569</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.003672717914022186</v>
+        <v>0.003619490118166791</v>
       </c>
       <c r="W70">
-        <v>0.2349339731158736</v>
+        <v>0.2349465242301363</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.0193300942843273</v>
+        <v>0.01904994799035153</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7169,22 +7169,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2286269293787598</v>
+        <v>0.2305269293787598</v>
       </c>
       <c r="C71">
-        <v>-12.87482571247988</v>
+        <v>-13.28841408812222</v>
       </c>
       <c r="D71">
-        <v>9.156464287520121</v>
+        <v>9.062285911877787</v>
       </c>
       <c r="E71">
-        <v>21.69829</v>
+        <v>22.0177</v>
       </c>
       <c r="F71">
-        <v>22.03929</v>
+        <v>22.3587</v>
       </c>
       <c r="G71">
         <v>0.008</v>
@@ -7205,37 +7205,37 @@
         <v>0.099</v>
       </c>
       <c r="M71">
-        <v>5.196864582000002</v>
+        <v>5.272181460000001</v>
       </c>
       <c r="N71">
-        <v>-5.097864582000001</v>
+        <v>-5.17318146</v>
       </c>
       <c r="O71">
-        <v>-0.9685942705800002</v>
+        <v>-0.9829044774000001</v>
       </c>
       <c r="P71">
-        <v>-4.129270311420001</v>
+        <v>-4.1902769826</v>
       </c>
       <c r="Q71">
-        <v>-4.228270311420001</v>
+        <v>-4.289276982600001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2145607343869862</v>
+        <v>0.2201860921998857</v>
       </c>
       <c r="T71">
-        <v>3.090912116619569</v>
+        <v>3.193942520506888</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.003619490118166791</v>
+        <v>0.003567783116478695</v>
       </c>
       <c r="W71">
-        <v>0.2349465242301363</v>
+        <v>0.2349587167411343</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.01904994799035153</v>
+        <v>0.0187778058762037</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7251,22 +7251,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2305269293787598</v>
+        <v>0.2324269293787598</v>
       </c>
       <c r="C72">
-        <v>-13.28841408812222</v>
+        <v>-13.70008485289975</v>
       </c>
       <c r="D72">
-        <v>9.062285911877787</v>
+        <v>8.970025147100252</v>
       </c>
       <c r="E72">
-        <v>22.0177</v>
+        <v>22.33711</v>
       </c>
       <c r="F72">
-        <v>22.3587</v>
+        <v>22.67811</v>
       </c>
       <c r="G72">
         <v>0.008</v>
@@ -7287,37 +7287,37 @@
         <v>0.099</v>
       </c>
       <c r="M72">
-        <v>5.272181460000001</v>
+        <v>5.347498338000001</v>
       </c>
       <c r="N72">
-        <v>-5.17318146</v>
+        <v>-5.248498338000001</v>
       </c>
       <c r="O72">
-        <v>-0.9829044774000001</v>
+        <v>-0.9972146842200001</v>
       </c>
       <c r="P72">
-        <v>-4.1902769826</v>
+        <v>-4.251283653780001</v>
       </c>
       <c r="Q72">
-        <v>-4.289276982600001</v>
+        <v>-4.350283653780001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2201860921998857</v>
+        <v>0.2261994057240198</v>
       </c>
       <c r="T72">
-        <v>3.193942520506888</v>
+        <v>3.304078469489885</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.003567783116478695</v>
+        <v>0.003517532650049417</v>
       </c>
       <c r="W72">
-        <v>0.2349587167411343</v>
+        <v>0.2349705658011184</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.0187778058762037</v>
+        <v>0.01851332973710218</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7333,22 +7333,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2324269293787598</v>
+        <v>0.2343269293787598</v>
       </c>
       <c r="C73">
-        <v>-13.70008485289975</v>
+        <v>-14.10989598464073</v>
       </c>
       <c r="D73">
-        <v>8.970025147100252</v>
+        <v>8.879624015359276</v>
       </c>
       <c r="E73">
-        <v>22.33711</v>
+        <v>22.65652</v>
       </c>
       <c r="F73">
-        <v>22.67811</v>
+        <v>22.99752</v>
       </c>
       <c r="G73">
         <v>0.008</v>
@@ -7369,37 +7369,37 @@
         <v>0.099</v>
       </c>
       <c r="M73">
-        <v>5.347498338</v>
+        <v>5.422815216000001</v>
       </c>
       <c r="N73">
-        <v>-5.248498338</v>
+        <v>-5.323815216000001</v>
       </c>
       <c r="O73">
-        <v>-0.99721468422</v>
+        <v>-1.01152489104</v>
       </c>
       <c r="P73">
-        <v>-4.25128365378</v>
+        <v>-4.312290324960001</v>
       </c>
       <c r="Q73">
-        <v>-4.35028365378</v>
+        <v>-4.411290324960001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2261994057240197</v>
+        <v>0.2326422416427347</v>
       </c>
       <c r="T73">
-        <v>3.304078469489883</v>
+        <v>3.422081271971665</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.003517532650049418</v>
+        <v>0.003468678029909842</v>
       </c>
       <c r="W73">
-        <v>0.2349705658011184</v>
+        <v>0.2349820857205473</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.01851332973710229</v>
+        <v>0.01825620015742024</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7415,22 +7415,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2343269293787598</v>
+        <v>0.2362269293787597</v>
       </c>
       <c r="C74">
-        <v>-14.10989598464073</v>
+        <v>-14.5179031472596</v>
       </c>
       <c r="D74">
-        <v>8.879624015359276</v>
+        <v>8.791026852740403</v>
       </c>
       <c r="E74">
-        <v>22.65652</v>
+        <v>22.97593</v>
       </c>
       <c r="F74">
-        <v>22.99752</v>
+        <v>23.31693</v>
       </c>
       <c r="G74">
         <v>0.008</v>
@@ -7451,37 +7451,37 @@
         <v>0.099</v>
       </c>
       <c r="M74">
-        <v>5.422815216000001</v>
+        <v>5.498132094000001</v>
       </c>
       <c r="N74">
-        <v>-5.323815216000001</v>
+        <v>-5.399132094</v>
       </c>
       <c r="O74">
-        <v>-1.01152489104</v>
+        <v>-1.02583509786</v>
       </c>
       <c r="P74">
-        <v>-4.312290324960001</v>
+        <v>-4.373296996140001</v>
       </c>
       <c r="Q74">
-        <v>-4.411290324960001</v>
+        <v>-4.472296996140001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2326422416427347</v>
+        <v>0.2395623246665396</v>
       </c>
       <c r="T74">
-        <v>3.422081271971665</v>
+        <v>3.54882502278543</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.003468678029909842</v>
+        <v>0.003421161892513817</v>
       </c>
       <c r="W74">
-        <v>0.2349820857205473</v>
+        <v>0.2349932900257452</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.01825620015742024</v>
+        <v>0.01800611522375695</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7497,22 +7497,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2362269293787597</v>
+        <v>0.2381269293787597</v>
       </c>
       <c r="C75">
-        <v>-14.5179031472596</v>
+        <v>-14.92415980505297</v>
       </c>
       <c r="D75">
-        <v>8.791026852740403</v>
+        <v>8.704180194947034</v>
       </c>
       <c r="E75">
-        <v>22.97593</v>
+        <v>23.29534</v>
       </c>
       <c r="F75">
-        <v>23.31693</v>
+        <v>23.63634</v>
       </c>
       <c r="G75">
         <v>0.008</v>
@@ -7533,37 +7533,37 @@
         <v>0.099</v>
       </c>
       <c r="M75">
-        <v>5.498132094000001</v>
+        <v>5.573448972</v>
       </c>
       <c r="N75">
-        <v>-5.399132094</v>
+        <v>-5.474448972</v>
       </c>
       <c r="O75">
-        <v>-1.02583509786</v>
+        <v>-1.04014530468</v>
       </c>
       <c r="P75">
-        <v>-4.373296996140001</v>
+        <v>-4.43430366732</v>
       </c>
       <c r="Q75">
-        <v>-4.472296996140001</v>
+        <v>-4.53330366732</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2395623246665396</v>
+        <v>0.2470147217690989</v>
       </c>
       <c r="T75">
-        <v>3.54882502278543</v>
+        <v>3.685318292892562</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.003421161892513817</v>
+        <v>0.003374929975047415</v>
       </c>
       <c r="W75">
-        <v>0.2349932900257452</v>
+        <v>0.2350041915118838</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.01800611522375695</v>
+        <v>0.01776278934235487</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7579,22 +7579,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2381269293787597</v>
+        <v>0.2400269293787597</v>
       </c>
       <c r="C76">
-        <v>-14.92415980505297</v>
+        <v>-15.32871733028697</v>
       </c>
       <c r="D76">
-        <v>8.704180194947034</v>
+        <v>8.619032669713038</v>
       </c>
       <c r="E76">
-        <v>23.29534</v>
+        <v>23.61475</v>
       </c>
       <c r="F76">
-        <v>23.63634</v>
+        <v>23.95575</v>
       </c>
       <c r="G76">
         <v>0.008</v>
@@ -7615,37 +7615,37 @@
         <v>0.099</v>
       </c>
       <c r="M76">
-        <v>5.573448972</v>
+        <v>5.648765850000001</v>
       </c>
       <c r="N76">
-        <v>-5.474448972</v>
+        <v>-5.549765850000001</v>
       </c>
       <c r="O76">
-        <v>-1.04014530468</v>
+        <v>-1.0544555115</v>
       </c>
       <c r="P76">
-        <v>-4.43430366732</v>
+        <v>-4.4953103385</v>
       </c>
       <c r="Q76">
-        <v>-4.53330366732</v>
+        <v>-4.594310338500001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2470147217690989</v>
+        <v>0.2550633106398628</v>
       </c>
       <c r="T76">
-        <v>3.685318292892562</v>
+        <v>3.832731024608265</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.003374929975047415</v>
+        <v>0.003329930908713449</v>
       </c>
       <c r="W76">
-        <v>0.2350041915118838</v>
+        <v>0.2350148022917254</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.01776278934235487</v>
+        <v>0.0175259521511234</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2400269293787597</v>
+        <v>0.2419269293787597</v>
       </c>
       <c r="C77">
-        <v>-15.32871733028697</v>
+        <v>-15.73162510453106</v>
       </c>
       <c r="D77">
-        <v>8.619032669713038</v>
+        <v>8.535534895468945</v>
       </c>
       <c r="E77">
-        <v>23.61475</v>
+        <v>23.93416</v>
       </c>
       <c r="F77">
-        <v>23.95575</v>
+        <v>24.27516</v>
       </c>
       <c r="G77">
         <v>0.008</v>
@@ -7697,37 +7697,37 @@
         <v>0.099</v>
       </c>
       <c r="M77">
-        <v>5.648765850000001</v>
+        <v>5.724082728000001</v>
       </c>
       <c r="N77">
-        <v>-5.549765850000001</v>
+        <v>-5.625082728000001</v>
       </c>
       <c r="O77">
-        <v>-1.0544555115</v>
+        <v>-1.06876571832</v>
       </c>
       <c r="P77">
-        <v>-4.4953103385</v>
+        <v>-4.556317009680001</v>
       </c>
       <c r="Q77">
-        <v>-4.594310338500001</v>
+        <v>-4.655317009680001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2550633106398628</v>
+        <v>0.2637826152498571</v>
       </c>
       <c r="T77">
-        <v>3.832731024608265</v>
+        <v>3.99242815063361</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.003329930908713449</v>
+        <v>0.003286116028335641</v>
       </c>
       <c r="W77">
-        <v>0.2350148022917254</v>
+        <v>0.2350251338405185</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.0175259521511234</v>
+        <v>0.01729534751755601</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7743,22 +7743,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2419269293787597</v>
+        <v>0.2438269293787597</v>
       </c>
       <c r="C78">
-        <v>-15.73162510453106</v>
+        <v>-16.1329306141583</v>
       </c>
       <c r="D78">
-        <v>8.535534895468945</v>
+        <v>8.453639385841706</v>
       </c>
       <c r="E78">
-        <v>23.93416</v>
+        <v>24.25357</v>
       </c>
       <c r="F78">
-        <v>24.27516</v>
+        <v>24.59457</v>
       </c>
       <c r="G78">
         <v>0.008</v>
@@ -7779,37 +7779,37 @@
         <v>0.099</v>
       </c>
       <c r="M78">
-        <v>5.724082728000001</v>
+        <v>5.799399606000001</v>
       </c>
       <c r="N78">
-        <v>-5.625082728000001</v>
+        <v>-5.700399606</v>
       </c>
       <c r="O78">
-        <v>-1.06876571832</v>
+        <v>-1.08307592514</v>
       </c>
       <c r="P78">
-        <v>-4.556317009680001</v>
+        <v>-4.61732368086</v>
       </c>
       <c r="Q78">
-        <v>-4.655317009680001</v>
+        <v>-4.71632368086</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2637826152498571</v>
+        <v>0.2732601202607204</v>
       </c>
       <c r="T78">
-        <v>3.99242815063361</v>
+        <v>4.166011983269853</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.003286116028335641</v>
+        <v>0.003243439196798814</v>
       </c>
       <c r="W78">
-        <v>0.2350251338405185</v>
+        <v>0.2350351970373948</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.01729534751755601</v>
+        <v>0.01707073261473069</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7825,22 +7825,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2438269293787597</v>
+        <v>0.2457269293787598</v>
       </c>
       <c r="C79">
-        <v>-16.1329306141583</v>
+        <v>-16.53267954040005</v>
       </c>
       <c r="D79">
-        <v>8.453639385841706</v>
+        <v>8.373300459599957</v>
       </c>
       <c r="E79">
-        <v>24.25357</v>
+        <v>24.57298</v>
       </c>
       <c r="F79">
-        <v>24.59457</v>
+        <v>24.91398</v>
       </c>
       <c r="G79">
         <v>0.008</v>
@@ -7861,37 +7861,37 @@
         <v>0.099</v>
       </c>
       <c r="M79">
-        <v>5.799399606000001</v>
+        <v>5.874716484</v>
       </c>
       <c r="N79">
-        <v>-5.700399606</v>
+        <v>-5.775716484</v>
       </c>
       <c r="O79">
-        <v>-1.08307592514</v>
+        <v>-1.09738613196</v>
       </c>
       <c r="P79">
-        <v>-4.61732368086</v>
+        <v>-4.67833035204</v>
       </c>
       <c r="Q79">
-        <v>-4.71632368086</v>
+        <v>-4.77733035204</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2732601202607204</v>
+        <v>0.2835992166362078</v>
       </c>
       <c r="T79">
-        <v>4.166011983269853</v>
+        <v>4.355376164327574</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.003243439196798814</v>
+        <v>0.003201856642993701</v>
       </c>
       <c r="W79">
-        <v>0.2350351970373948</v>
+        <v>0.2350450022035821</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.01707073261473069</v>
+        <v>0.01685187706838798</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7907,22 +7907,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2457269293787598</v>
+        <v>0.2476269293787597</v>
       </c>
       <c r="C80">
-        <v>-16.53267954040005</v>
+        <v>-16.93091584431405</v>
       </c>
       <c r="D80">
-        <v>8.373300459599957</v>
+        <v>8.294474155685956</v>
       </c>
       <c r="E80">
-        <v>24.57298</v>
+        <v>24.89239</v>
       </c>
       <c r="F80">
-        <v>24.91398</v>
+        <v>25.23339</v>
       </c>
       <c r="G80">
         <v>0.008</v>
@@ -7943,37 +7943,37 @@
         <v>0.099</v>
       </c>
       <c r="M80">
-        <v>5.874716484</v>
+        <v>5.950033362000001</v>
       </c>
       <c r="N80">
-        <v>-5.775716484</v>
+        <v>-5.851033362000001</v>
       </c>
       <c r="O80">
-        <v>-1.09738613196</v>
+        <v>-1.11169633878</v>
       </c>
       <c r="P80">
-        <v>-4.67833035204</v>
+        <v>-4.739337023220001</v>
       </c>
       <c r="Q80">
-        <v>-4.77733035204</v>
+        <v>-4.838337023220001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2835992166362078</v>
+        <v>0.2949229888569796</v>
       </c>
       <c r="T80">
-        <v>4.355376164327574</v>
+        <v>4.562775029295555</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.003201856642993701</v>
+        <v>0.00316132681206973</v>
       </c>
       <c r="W80">
-        <v>0.2350450022035821</v>
+        <v>0.235054559137714</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.01685187706838798</v>
+        <v>0.01663856216878812</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7989,22 +7989,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2476269293787597</v>
+        <v>0.2495269293787598</v>
       </c>
       <c r="C81">
-        <v>-16.93091584431405</v>
+        <v>-17.32768184699793</v>
       </c>
       <c r="D81">
-        <v>8.294474155685956</v>
+        <v>8.217118153002071</v>
       </c>
       <c r="E81">
-        <v>24.89239</v>
+        <v>25.2118</v>
       </c>
       <c r="F81">
-        <v>25.23339</v>
+        <v>25.5528</v>
       </c>
       <c r="G81">
         <v>0.008</v>
@@ -8025,37 +8025,37 @@
         <v>0.099</v>
       </c>
       <c r="M81">
-        <v>5.950033362000001</v>
+        <v>6.025350240000002</v>
       </c>
       <c r="N81">
-        <v>-5.851033362000001</v>
+        <v>-5.926350240000001</v>
       </c>
       <c r="O81">
-        <v>-1.11169633878</v>
+        <v>-1.1260065456</v>
       </c>
       <c r="P81">
-        <v>-4.739337023220001</v>
+        <v>-4.800343694400001</v>
       </c>
       <c r="Q81">
-        <v>-4.838337023220001</v>
+        <v>-4.899343694400002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2949229888569796</v>
+        <v>0.3073791382998286</v>
       </c>
       <c r="T81">
-        <v>4.562775029295555</v>
+        <v>4.790913780760333</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.00316132681206973</v>
+        <v>0.003121810226918858</v>
       </c>
       <c r="W81">
-        <v>0.235054559137714</v>
+        <v>0.2350638771484926</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.01663856216878812</v>
+        <v>0.0164305801416782</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8071,22 +8071,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2495269293787598</v>
+        <v>0.2514269293787597</v>
       </c>
       <c r="C82">
-        <v>-17.32768184699793</v>
+        <v>-17.72301830535566</v>
       </c>
       <c r="D82">
-        <v>8.217118153002071</v>
+        <v>8.141191694644343</v>
       </c>
       <c r="E82">
-        <v>25.2118</v>
+        <v>25.53121</v>
       </c>
       <c r="F82">
-        <v>25.5528</v>
+        <v>25.87221</v>
       </c>
       <c r="G82">
         <v>0.008</v>
@@ -8107,37 +8107,37 @@
         <v>0.099</v>
       </c>
       <c r="M82">
-        <v>6.025350240000002</v>
+        <v>6.100667118</v>
       </c>
       <c r="N82">
-        <v>-5.926350240000001</v>
+        <v>-6.001667118</v>
       </c>
       <c r="O82">
-        <v>-1.1260065456</v>
+        <v>-1.14031675242</v>
       </c>
       <c r="P82">
-        <v>-4.800343694400001</v>
+        <v>-4.86135036558</v>
       </c>
       <c r="Q82">
-        <v>-4.899343694400002</v>
+        <v>-4.96035036558</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3073791382998286</v>
+        <v>0.3211464613682407</v>
       </c>
       <c r="T82">
-        <v>4.790913780760333</v>
+        <v>5.043067137642455</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.003121810226918858</v>
+        <v>0.00308326935991986</v>
       </c>
       <c r="W82">
-        <v>0.2350638771484926</v>
+        <v>0.2350729650849309</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.0164305801416782</v>
+        <v>0.01622773347326245</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8153,22 +8153,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2514269293787597</v>
+        <v>0.2533269293787598</v>
       </c>
       <c r="C83">
-        <v>-17.72301830535566</v>
+        <v>-18.11696448370191</v>
       </c>
       <c r="D83">
-        <v>8.141191694644343</v>
+        <v>8.066655516298093</v>
       </c>
       <c r="E83">
-        <v>25.53121</v>
+        <v>25.85062</v>
       </c>
       <c r="F83">
-        <v>25.87221</v>
+        <v>26.19162</v>
       </c>
       <c r="G83">
         <v>0.008</v>
@@ -8189,37 +8189,37 @@
         <v>0.099</v>
       </c>
       <c r="M83">
-        <v>6.100667118</v>
+        <v>6.175983996000001</v>
       </c>
       <c r="N83">
-        <v>-6.001667118</v>
+        <v>-6.076983996000001</v>
       </c>
       <c r="O83">
-        <v>-1.14031675242</v>
+        <v>-1.15462695924</v>
       </c>
       <c r="P83">
-        <v>-4.86135036558</v>
+        <v>-4.922357036760001</v>
       </c>
       <c r="Q83">
-        <v>-4.96035036558</v>
+        <v>-5.021357036760001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3211464613682407</v>
+        <v>0.3364434869998096</v>
       </c>
       <c r="T83">
-        <v>5.043067137642455</v>
+        <v>5.323237534178148</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.00308326935991986</v>
+        <v>0.003045668514067179</v>
       </c>
       <c r="W83">
-        <v>0.2350729650849309</v>
+        <v>0.235081831364383</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.01622773347326245</v>
+        <v>0.01602983428456417</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8235,22 +8235,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2533269293787598</v>
+        <v>0.2552269293787597</v>
       </c>
       <c r="C84">
-        <v>-18.11696448370191</v>
+        <v>-18.50955822146873</v>
       </c>
       <c r="D84">
-        <v>8.066655516298093</v>
+        <v>7.993471778531272</v>
       </c>
       <c r="E84">
-        <v>25.85062</v>
+        <v>26.17003</v>
       </c>
       <c r="F84">
-        <v>26.19162</v>
+        <v>26.51103000000001</v>
       </c>
       <c r="G84">
         <v>0.008</v>
@@ -8271,37 +8271,37 @@
         <v>0.099</v>
       </c>
       <c r="M84">
-        <v>6.175983996000001</v>
+        <v>6.251300874000002</v>
       </c>
       <c r="N84">
-        <v>-6.076983996000001</v>
+        <v>-6.152300874000002</v>
       </c>
       <c r="O84">
-        <v>-1.15462695924</v>
+        <v>-1.16893716606</v>
       </c>
       <c r="P84">
-        <v>-4.922357036760001</v>
+        <v>-4.983363707940001</v>
       </c>
       <c r="Q84">
-        <v>-5.021357036760001</v>
+        <v>-5.082363707940002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3364434869998096</v>
+        <v>0.3535401627056808</v>
       </c>
       <c r="T84">
-        <v>5.323237534178148</v>
+        <v>5.636369153835687</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.003045668514067179</v>
+        <v>0.003008973712692875</v>
       </c>
       <c r="W84">
-        <v>0.235081831364383</v>
+        <v>0.235090483998547</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.01602983428456417</v>
+        <v>0.0158367037510152</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8317,22 +8317,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2552269293787597</v>
+        <v>0.2571269293787597</v>
       </c>
       <c r="C85">
-        <v>-18.50955822146873</v>
+        <v>-18.90083599725981</v>
       </c>
       <c r="D85">
-        <v>7.993471778531272</v>
+        <v>7.921604002740193</v>
       </c>
       <c r="E85">
-        <v>26.17003</v>
+        <v>26.48944</v>
       </c>
       <c r="F85">
-        <v>26.51103000000001</v>
+        <v>26.83044</v>
       </c>
       <c r="G85">
         <v>0.008</v>
@@ -8353,37 +8353,37 @@
         <v>0.099</v>
       </c>
       <c r="M85">
-        <v>6.251300874000002</v>
+        <v>6.326617752000001</v>
       </c>
       <c r="N85">
-        <v>-6.152300874000002</v>
+        <v>-6.227617752</v>
       </c>
       <c r="O85">
-        <v>-1.16893716606</v>
+        <v>-1.18324737288</v>
       </c>
       <c r="P85">
-        <v>-4.983363707940001</v>
+        <v>-5.04437037912</v>
       </c>
       <c r="Q85">
-        <v>-5.082363707940002</v>
+        <v>-5.14337037912</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3535401627056808</v>
+        <v>0.3727739228747859</v>
       </c>
       <c r="T85">
-        <v>5.636369153835687</v>
+        <v>5.988642225950418</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.003008973712692875</v>
+        <v>0.00297315259706558</v>
       </c>
       <c r="W85">
-        <v>0.235090483998547</v>
+        <v>0.2350989306176119</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.0158367037510152</v>
+        <v>0.01564817156350307</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8399,22 +8399,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2571269293787597</v>
+        <v>0.2590269293787597</v>
       </c>
       <c r="C86">
-        <v>-18.9008359972598</v>
+        <v>-19.29083298948006</v>
       </c>
       <c r="D86">
-        <v>7.921604002740193</v>
+        <v>7.851017010519945</v>
       </c>
       <c r="E86">
-        <v>26.48944</v>
+        <v>26.80885</v>
       </c>
       <c r="F86">
-        <v>26.83044</v>
+        <v>27.14985</v>
       </c>
       <c r="G86">
         <v>0.008</v>
@@ -8435,37 +8435,37 @@
         <v>0.099</v>
       </c>
       <c r="M86">
-        <v>6.326617752</v>
+        <v>6.40193463</v>
       </c>
       <c r="N86">
-        <v>-6.227617752</v>
+        <v>-6.30293463</v>
       </c>
       <c r="O86">
-        <v>-1.18324737288</v>
+        <v>-1.1975575797</v>
       </c>
       <c r="P86">
-        <v>-5.04437037912</v>
+        <v>-5.1053770503</v>
       </c>
       <c r="Q86">
-        <v>-5.14337037912</v>
+        <v>-5.204377050300001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3727739228747857</v>
+        <v>0.3945721843997714</v>
       </c>
       <c r="T86">
-        <v>5.988642225950414</v>
+        <v>6.387885041013775</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.00297315259706558</v>
+        <v>0.002938174331217749</v>
       </c>
       <c r="W86">
-        <v>0.2350989306176119</v>
+        <v>0.2351071784926989</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.01564817156350307</v>
+        <v>0.01546407542746187</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8481,22 +8481,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2590269293787597</v>
+        <v>0.2609269293787597</v>
       </c>
       <c r="C87">
-        <v>-19.29083298948006</v>
+        <v>-19.67958313375239</v>
       </c>
       <c r="D87">
-        <v>7.851017010519945</v>
+        <v>7.781676866247609</v>
       </c>
       <c r="E87">
-        <v>26.80885</v>
+        <v>27.12826</v>
       </c>
       <c r="F87">
-        <v>27.14985</v>
+        <v>27.46926</v>
       </c>
       <c r="G87">
         <v>0.008</v>
@@ -8517,37 +8517,37 @@
         <v>0.099</v>
       </c>
       <c r="M87">
-        <v>6.40193463</v>
+        <v>6.477251508000001</v>
       </c>
       <c r="N87">
-        <v>-6.30293463</v>
+        <v>-6.378251508000001</v>
       </c>
       <c r="O87">
-        <v>-1.1975575797</v>
+        <v>-1.21186778652</v>
       </c>
       <c r="P87">
-        <v>-5.1053770503</v>
+        <v>-5.166383721480001</v>
       </c>
       <c r="Q87">
-        <v>-5.204377050300001</v>
+        <v>-5.265383721480001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3945721843997714</v>
+        <v>0.4194844832854693</v>
       </c>
       <c r="T87">
-        <v>6.387885041013775</v>
+        <v>6.84416254394333</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.002938174331217749</v>
+        <v>0.002904009513412892</v>
       </c>
       <c r="W87">
-        <v>0.2351071784926989</v>
+        <v>0.2351152345567372</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.01546407542746187</v>
+        <v>0.01528426059691002</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8563,22 +8563,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2609269293787597</v>
+        <v>0.2628269293787597</v>
       </c>
       <c r="C88">
-        <v>-19.67958313375239</v>
+        <v>-20.06711917731848</v>
       </c>
       <c r="D88">
-        <v>7.781676866247609</v>
+        <v>7.713550822681524</v>
       </c>
       <c r="E88">
-        <v>27.12826</v>
+        <v>27.44767</v>
       </c>
       <c r="F88">
-        <v>27.46926</v>
+        <v>27.78867</v>
       </c>
       <c r="G88">
         <v>0.008</v>
@@ -8599,37 +8599,37 @@
         <v>0.099</v>
       </c>
       <c r="M88">
-        <v>6.477251508000001</v>
+        <v>6.552568386000001</v>
       </c>
       <c r="N88">
-        <v>-6.378251508000001</v>
+        <v>-6.453568386000001</v>
       </c>
       <c r="O88">
-        <v>-1.21186778652</v>
+        <v>-1.22617799334</v>
       </c>
       <c r="P88">
-        <v>-5.166383721480001</v>
+        <v>-5.22739039266</v>
       </c>
       <c r="Q88">
-        <v>-5.265383721480001</v>
+        <v>-5.32639039266</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4194844832854693</v>
+        <v>0.4482294435381977</v>
       </c>
       <c r="T88">
-        <v>6.84416254394333</v>
+        <v>7.370636585785125</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.002904009513412892</v>
+        <v>0.002870630093718491</v>
       </c>
       <c r="W88">
-        <v>0.2351152345567372</v>
+        <v>0.2351231054239012</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.01528426059691002</v>
+        <v>0.01510857944062372</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8645,22 +8645,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2628269293787597</v>
+        <v>0.2647269293787597</v>
       </c>
       <c r="C89">
-        <v>-20.06711917731848</v>
+        <v>-20.4534727306067</v>
       </c>
       <c r="D89">
-        <v>7.713550822681524</v>
+        <v>7.646607269393298</v>
       </c>
       <c r="E89">
-        <v>27.44767</v>
+        <v>27.76708</v>
       </c>
       <c r="F89">
-        <v>27.78867</v>
+        <v>28.10808</v>
       </c>
       <c r="G89">
         <v>0.008</v>
@@ -8681,37 +8681,37 @@
         <v>0.099</v>
       </c>
       <c r="M89">
-        <v>6.552568386000001</v>
+        <v>6.627885264000001</v>
       </c>
       <c r="N89">
-        <v>-6.453568386000001</v>
+        <v>-6.528885264</v>
       </c>
       <c r="O89">
-        <v>-1.22617799334</v>
+        <v>-1.24048820016</v>
       </c>
       <c r="P89">
-        <v>-5.22739039266</v>
+        <v>-5.28839706384</v>
       </c>
       <c r="Q89">
-        <v>-5.32639039266</v>
+        <v>-5.38739706384</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4482294435381977</v>
+        <v>0.4817652304997143</v>
       </c>
       <c r="T89">
-        <v>7.370636585785125</v>
+        <v>7.984856301267221</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.002870630093718491</v>
+        <v>0.002838009297198962</v>
       </c>
       <c r="W89">
-        <v>0.2351231054239012</v>
+        <v>0.2351307974077205</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.01510857944062372</v>
+        <v>0.01493689103788931</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8727,22 +8727,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2647269293787597</v>
+        <v>0.2666269293787598</v>
       </c>
       <c r="C90">
-        <v>-20.4534727306067</v>
+        <v>-20.83867431613805</v>
       </c>
       <c r="D90">
-        <v>7.646607269393298</v>
+        <v>7.58081568386195</v>
       </c>
       <c r="E90">
-        <v>27.76708</v>
+        <v>28.08649</v>
       </c>
       <c r="F90">
-        <v>28.10808</v>
+        <v>28.42749</v>
       </c>
       <c r="G90">
         <v>0.008</v>
@@ -8763,37 +8763,37 @@
         <v>0.099</v>
       </c>
       <c r="M90">
-        <v>6.627885264000001</v>
+        <v>6.703202142000001</v>
       </c>
       <c r="N90">
-        <v>-6.528885264</v>
+        <v>-6.604202142000001</v>
       </c>
       <c r="O90">
-        <v>-1.24048820016</v>
+        <v>-1.25479840698</v>
       </c>
       <c r="P90">
-        <v>-5.28839706384</v>
+        <v>-5.349403735020001</v>
       </c>
       <c r="Q90">
-        <v>-5.38739706384</v>
+        <v>-5.448403735020001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4817652304997143</v>
+        <v>0.5213984332724155</v>
       </c>
       <c r="T90">
-        <v>7.984856301267221</v>
+        <v>8.710752328655149</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.002838009297198962</v>
+        <v>0.002806121552286614</v>
       </c>
       <c r="W90">
-        <v>0.2351307974077205</v>
+        <v>0.2351383165379708</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.01493689103788931</v>
+        <v>0.01476906080150853</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8809,22 +8809,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2666269293787598</v>
+        <v>0.2685269293787598</v>
       </c>
       <c r="C91">
-        <v>-20.83867431613805</v>
+        <v>-21.22275341492873</v>
       </c>
       <c r="D91">
-        <v>7.58081568386195</v>
+        <v>7.516146585071279</v>
       </c>
       <c r="E91">
-        <v>28.08649</v>
+        <v>28.4059</v>
       </c>
       <c r="F91">
-        <v>28.42749</v>
+        <v>28.7469</v>
       </c>
       <c r="G91">
         <v>0.008</v>
@@ -8845,37 +8845,37 @@
         <v>0.099</v>
       </c>
       <c r="M91">
-        <v>6.703202142000001</v>
+        <v>6.778519020000001</v>
       </c>
       <c r="N91">
-        <v>-6.604202142000001</v>
+        <v>-6.679519020000001</v>
       </c>
       <c r="O91">
-        <v>-1.25479840698</v>
+        <v>-1.2691086138</v>
       </c>
       <c r="P91">
-        <v>-5.349403735020001</v>
+        <v>-5.4104104062</v>
       </c>
       <c r="Q91">
-        <v>-5.448403735020001</v>
+        <v>-5.509410406200001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5213984332724155</v>
+        <v>0.5689582765996571</v>
       </c>
       <c r="T91">
-        <v>8.710752328655149</v>
+        <v>9.581827561520665</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.002806121552286614</v>
+        <v>0.002774942423927874</v>
       </c>
       <c r="W91">
-        <v>0.2351383165379708</v>
+        <v>0.2351456685764378</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.01476906080150853</v>
+        <v>0.01460496012593626</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8891,22 +8891,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2685269293787598</v>
+        <v>0.2704269293787597</v>
       </c>
       <c r="C92">
-        <v>-21.22275341492873</v>
+        <v>-21.60573851053783</v>
       </c>
       <c r="D92">
-        <v>7.516146585071279</v>
+        <v>7.452571489462171</v>
       </c>
       <c r="E92">
-        <v>28.4059</v>
+        <v>28.72531</v>
       </c>
       <c r="F92">
-        <v>28.7469</v>
+        <v>29.06631</v>
       </c>
       <c r="G92">
         <v>0.008</v>
@@ -8927,37 +8927,37 @@
         <v>0.099</v>
       </c>
       <c r="M92">
-        <v>6.778519020000001</v>
+        <v>6.853835898000002</v>
       </c>
       <c r="N92">
-        <v>-6.679519020000001</v>
+        <v>-6.754835898000001</v>
       </c>
       <c r="O92">
-        <v>-1.2691086138</v>
+        <v>-1.28341882062</v>
       </c>
       <c r="P92">
-        <v>-5.4104104062</v>
+        <v>-5.471417077380001</v>
       </c>
       <c r="Q92">
-        <v>-5.509410406200001</v>
+        <v>-5.570417077380001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5689582765996571</v>
+        <v>0.6270869739996191</v>
       </c>
       <c r="T92">
-        <v>9.581827561520665</v>
+        <v>10.6464750683563</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.002774942423927874</v>
+        <v>0.002744448551137458</v>
       </c>
       <c r="W92">
-        <v>0.2351456685764378</v>
+        <v>0.2351528590316418</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.01460496012593626</v>
+        <v>0.01444446605861827</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8973,22 +8973,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2704269293787597</v>
+        <v>0.2723269293787597</v>
       </c>
       <c r="C93">
-        <v>-21.60573851053783</v>
+        <v>-21.98765713089838</v>
       </c>
       <c r="D93">
-        <v>7.452571489462171</v>
+        <v>7.390062869101622</v>
       </c>
       <c r="E93">
-        <v>28.72531</v>
+        <v>29.04472</v>
       </c>
       <c r="F93">
-        <v>29.06631</v>
+        <v>29.38572</v>
       </c>
       <c r="G93">
         <v>0.008</v>
@@ -9009,37 +9009,37 @@
         <v>0.099</v>
       </c>
       <c r="M93">
-        <v>6.853835898000002</v>
+        <v>6.929152776000001</v>
       </c>
       <c r="N93">
-        <v>-6.754835898000001</v>
+        <v>-6.830152776000001</v>
       </c>
       <c r="O93">
-        <v>-1.28341882062</v>
+        <v>-1.29772902744</v>
       </c>
       <c r="P93">
-        <v>-5.471417077380001</v>
+        <v>-5.532423748560001</v>
       </c>
       <c r="Q93">
-        <v>-5.570417077380001</v>
+        <v>-5.631423748560001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6270869739996191</v>
+        <v>0.6997478457495716</v>
       </c>
       <c r="T93">
-        <v>10.6464750683563</v>
+        <v>11.97728445190083</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.002744448551137458</v>
+        <v>0.002714617588625094</v>
       </c>
       <c r="W93">
-        <v>0.2351528590316418</v>
+        <v>0.2351598931726022</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.01444446605861827</v>
+        <v>0.01428746099276368</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9055,22 +9055,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2723269293787597</v>
+        <v>0.2742269293787598</v>
       </c>
       <c r="C94">
-        <v>-21.98765713089838</v>
+        <v>-22.3685358880606</v>
       </c>
       <c r="D94">
-        <v>7.390062869101622</v>
+        <v>7.328594111939407</v>
       </c>
       <c r="E94">
-        <v>29.04472</v>
+        <v>29.36413</v>
       </c>
       <c r="F94">
-        <v>29.38572</v>
+        <v>29.70513</v>
       </c>
       <c r="G94">
         <v>0.008</v>
@@ -9091,37 +9091,37 @@
         <v>0.099</v>
       </c>
       <c r="M94">
-        <v>6.929152776000001</v>
+        <v>7.004469654000001</v>
       </c>
       <c r="N94">
-        <v>-6.830152776000001</v>
+        <v>-6.905469654000001</v>
       </c>
       <c r="O94">
-        <v>-1.29772902744</v>
+        <v>-1.31203923426</v>
       </c>
       <c r="P94">
-        <v>-5.532423748560001</v>
+        <v>-5.593430419740001</v>
       </c>
       <c r="Q94">
-        <v>-5.631423748560001</v>
+        <v>-5.692430419740001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6997478457495716</v>
+        <v>0.793168966570939</v>
       </c>
       <c r="T94">
-        <v>11.97728445190083</v>
+        <v>13.68832508788667</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.002714617588625094</v>
+        <v>0.002685428152188265</v>
       </c>
       <c r="W94">
-        <v>0.2351598931726022</v>
+        <v>0.235166776041714</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.01428746099276368</v>
+        <v>0.01413383237993826</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9137,22 +9137,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2742269293787598</v>
+        <v>0.2761269293787597</v>
       </c>
       <c r="C95">
-        <v>-22.3685358880606</v>
+        <v>-22.74840051596816</v>
       </c>
       <c r="D95">
-        <v>7.328594111939407</v>
+        <v>7.268139484031844</v>
       </c>
       <c r="E95">
-        <v>29.36413</v>
+        <v>29.68354</v>
       </c>
       <c r="F95">
-        <v>29.70513</v>
+        <v>30.02454000000001</v>
       </c>
       <c r="G95">
         <v>0.008</v>
@@ -9173,37 +9173,37 @@
         <v>0.099</v>
       </c>
       <c r="M95">
-        <v>7.004469654000001</v>
+        <v>7.079786532000002</v>
       </c>
       <c r="N95">
-        <v>-6.905469654000001</v>
+        <v>-6.980786532000002</v>
       </c>
       <c r="O95">
-        <v>-1.31203923426</v>
+        <v>-1.32634944108</v>
       </c>
       <c r="P95">
-        <v>-5.593430419740001</v>
+        <v>-5.654437090920001</v>
       </c>
       <c r="Q95">
-        <v>-5.692430419740001</v>
+        <v>-5.753437090920001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.793168966570939</v>
+        <v>0.9177304609994292</v>
       </c>
       <c r="T95">
-        <v>13.68832508788667</v>
+        <v>15.96971260253445</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.002685428152188265</v>
+        <v>0.002656859767590518</v>
       </c>
       <c r="W95">
-        <v>0.235166776041714</v>
+        <v>0.2351735124668022</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.01413383237993826</v>
+        <v>0.01398347246100273</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9219,22 +9219,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2761269293787597</v>
+        <v>0.2780269293787597</v>
       </c>
       <c r="C96">
-        <v>-22.74840051596816</v>
+        <v>-23.12727590638004</v>
       </c>
       <c r="D96">
-        <v>7.268139484031844</v>
+        <v>7.20867409361996</v>
       </c>
       <c r="E96">
-        <v>29.68354</v>
+        <v>30.00295</v>
       </c>
       <c r="F96">
-        <v>30.02454000000001</v>
+        <v>30.34395</v>
       </c>
       <c r="G96">
         <v>0.008</v>
@@ -9255,37 +9255,37 @@
         <v>0.099</v>
       </c>
       <c r="M96">
-        <v>7.079786532000002</v>
+        <v>7.155103410000001</v>
       </c>
       <c r="N96">
-        <v>-6.980786532000002</v>
+        <v>-7.05610341</v>
       </c>
       <c r="O96">
-        <v>-1.32634944108</v>
+        <v>-1.3406596479</v>
       </c>
       <c r="P96">
-        <v>-5.654437090920001</v>
+        <v>-5.7154437621</v>
       </c>
       <c r="Q96">
-        <v>-5.753437090920001</v>
+        <v>-5.814443762100001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9177304609994292</v>
+        <v>1.092116553199316</v>
       </c>
       <c r="T96">
-        <v>15.96971260253445</v>
+        <v>19.16365512304136</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.002656859767590518</v>
+        <v>0.002628892822668513</v>
       </c>
       <c r="W96">
-        <v>0.2351735124668022</v>
+        <v>0.2351801070724148</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.01398347246100273</v>
+        <v>0.01383627801404486</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9301,22 +9301,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2780269293787597</v>
+        <v>0.2799269293787598</v>
       </c>
       <c r="C97">
-        <v>-23.12727590638004</v>
+        <v>-23.50518614304321</v>
       </c>
       <c r="D97">
-        <v>7.20867409361996</v>
+        <v>7.150173856956791</v>
       </c>
       <c r="E97">
-        <v>30.00295</v>
+        <v>30.32236</v>
       </c>
       <c r="F97">
-        <v>30.34395</v>
+        <v>30.66336</v>
       </c>
       <c r="G97">
         <v>0.008</v>
@@ -9337,37 +9337,37 @@
         <v>0.099</v>
       </c>
       <c r="M97">
-        <v>7.155103410000001</v>
+        <v>7.230420288000001</v>
       </c>
       <c r="N97">
-        <v>-7.05610341</v>
+        <v>-7.131420288000001</v>
       </c>
       <c r="O97">
-        <v>-1.3406596479</v>
+        <v>-1.35496985472</v>
       </c>
       <c r="P97">
-        <v>-5.7154437621</v>
+        <v>-5.776450433280001</v>
       </c>
       <c r="Q97">
-        <v>-5.814443762100001</v>
+        <v>-5.875450433280001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.092116553199316</v>
+        <v>1.353695691499145</v>
       </c>
       <c r="T97">
-        <v>19.16365512304136</v>
+        <v>23.9545689038017</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.002628892822668513</v>
+        <v>0.002601508522432382</v>
       </c>
       <c r="W97">
-        <v>0.2351801070724148</v>
+        <v>0.2351865642904105</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.01383627801404486</v>
+        <v>0.01369215011806524</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9383,22 +9383,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2799269293787597</v>
+        <v>0.2818269293787597</v>
       </c>
       <c r="C98">
-        <v>-23.5051861430432</v>
+        <v>-23.88215453421482</v>
       </c>
       <c r="D98">
-        <v>7.150173856956795</v>
+        <v>7.09261546578518</v>
       </c>
       <c r="E98">
-        <v>30.32236</v>
+        <v>30.64177</v>
       </c>
       <c r="F98">
-        <v>30.66336</v>
+        <v>30.98277</v>
       </c>
       <c r="G98">
         <v>0.008</v>
@@ -9419,37 +9419,37 @@
         <v>0.099</v>
       </c>
       <c r="M98">
-        <v>7.230420288</v>
+        <v>7.305737166000001</v>
       </c>
       <c r="N98">
-        <v>-7.131420288</v>
+        <v>-7.206737166000001</v>
       </c>
       <c r="O98">
-        <v>-1.35496985472</v>
+        <v>-1.36928006154</v>
       </c>
       <c r="P98">
-        <v>-5.77645043328</v>
+        <v>-5.83745710446</v>
       </c>
       <c r="Q98">
-        <v>-5.87545043328</v>
+        <v>-5.936457104460001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.353695691499142</v>
+        <v>1.789660921998856</v>
       </c>
       <c r="T98">
-        <v>23.95456890380164</v>
+        <v>31.93942520506885</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.002601508522432382</v>
+        <v>0.002574688846943389</v>
       </c>
       <c r="W98">
-        <v>0.2351865642904105</v>
+        <v>0.2351928883698908</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.01369215011806524</v>
+        <v>0.01355099393128101</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9465,22 +9465,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2818269293787597</v>
+        <v>0.2837269293787597</v>
       </c>
       <c r="C99">
-        <v>-23.88215453421482</v>
+        <v>-24.25820364362618</v>
       </c>
       <c r="D99">
-        <v>7.09261546578518</v>
+        <v>7.035976356373824</v>
       </c>
       <c r="E99">
-        <v>30.64177</v>
+        <v>30.96118</v>
       </c>
       <c r="F99">
-        <v>30.98277</v>
+        <v>31.30218</v>
       </c>
       <c r="G99">
         <v>0.008</v>
@@ -9501,37 +9501,37 @@
         <v>0.099</v>
       </c>
       <c r="M99">
-        <v>7.305737166000001</v>
+        <v>7.381054044000001</v>
       </c>
       <c r="N99">
-        <v>-7.206737166000001</v>
+        <v>-7.282054044000001</v>
       </c>
       <c r="O99">
-        <v>-1.36928006154</v>
+        <v>-1.38359026836</v>
       </c>
       <c r="P99">
-        <v>-5.83745710446</v>
+        <v>-5.898463775640001</v>
       </c>
       <c r="Q99">
-        <v>-5.936457104460001</v>
+        <v>-5.997463775640001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.789660921998856</v>
+        <v>2.661591382998283</v>
       </c>
       <c r="T99">
-        <v>31.93942520506885</v>
+        <v>47.90913780760327</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.002574688846943389</v>
+        <v>0.002548416511770497</v>
       </c>
       <c r="W99">
-        <v>0.2351928883698908</v>
+        <v>0.2351990833865245</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.01355099393128101</v>
+        <v>0.01341271848300263</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9547,22 +9547,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2837269293787597</v>
+        <v>0.2856269293787597</v>
       </c>
       <c r="C100">
-        <v>-24.25820364362618</v>
+        <v>-24.63335531997478</v>
       </c>
       <c r="D100">
-        <v>7.035976356373824</v>
+        <v>6.980234680025218</v>
       </c>
       <c r="E100">
-        <v>30.96118</v>
+        <v>31.28059</v>
       </c>
       <c r="F100">
-        <v>31.30218</v>
+        <v>31.62159</v>
       </c>
       <c r="G100">
         <v>0.008</v>
@@ -9583,37 +9583,37 @@
         <v>0.099</v>
       </c>
       <c r="M100">
-        <v>7.381054044000001</v>
+        <v>7.456370922000001</v>
       </c>
       <c r="N100">
-        <v>-7.282054044000001</v>
+        <v>-7.357370922</v>
       </c>
       <c r="O100">
-        <v>-1.38359026836</v>
+        <v>-1.39790047518</v>
       </c>
       <c r="P100">
-        <v>-5.898463775640001</v>
+        <v>-5.95947044682</v>
       </c>
       <c r="Q100">
-        <v>-5.997463775640001</v>
+        <v>-6.05847044682</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.661591382998283</v>
+        <v>5.277382765996566</v>
       </c>
       <c r="T100">
-        <v>47.90913780760327</v>
+        <v>95.81827561520655</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.002548416511770497</v>
+        <v>0.002522674930843522</v>
       </c>
       <c r="W100">
-        <v>0.2351990833865245</v>
+        <v>0.2352051532513071</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9621,91 +9621,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.01341271848300263</v>
+        <v>0.01327723647812384</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2856269293787597</v>
-      </c>
-      <c r="C101">
-        <v>-24.63335531997478</v>
-      </c>
-      <c r="D101">
-        <v>6.980234680025218</v>
-      </c>
-      <c r="E101">
-        <v>31.28059</v>
-      </c>
-      <c r="F101">
-        <v>31.62159</v>
-      </c>
-      <c r="G101">
-        <v>0.008</v>
-      </c>
-      <c r="H101">
-        <v>31.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>-0.099</v>
-      </c>
-      <c r="L101">
-        <v>0.099</v>
-      </c>
-      <c r="M101">
-        <v>7.456370922000001</v>
-      </c>
-      <c r="N101">
-        <v>-7.357370922</v>
-      </c>
-      <c r="O101">
-        <v>-1.39790047518</v>
-      </c>
-      <c r="P101">
-        <v>-5.95947044682</v>
-      </c>
-      <c r="Q101">
-        <v>-6.05847044682</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.277382765996566</v>
-      </c>
-      <c r="T101">
-        <v>95.81827561520655</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.002522674930843522</v>
-      </c>
-      <c r="W101">
-        <v>0.2352051532513071</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.01327723647812384</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
